--- a/docs/Sprint_UseCase_Tracker.xlsx
+++ b/docs/Sprint_UseCase_Tracker.xlsx
@@ -15,6 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Use Cases'!$A$1:$K$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sprint Tasks'!$A$1:$M$121</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
 </workbook>
@@ -144,7 +145,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -235,6 +236,15 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -5729,19 +5739,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:M42"/>
+  <dimension ref="A1:M121"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="11" customWidth="1" style="15" min="1" max="1"/>
     <col width="12" customWidth="1" style="15" min="2" max="2"/>
-    <col width="26" customWidth="1" style="15" min="3" max="3"/>
-    <col width="12" customWidth="1" style="15" min="4" max="4"/>
-    <col width="30" customWidth="1" style="15" min="5" max="6"/>
+    <col width="34" customWidth="1" style="15" min="3" max="3"/>
+    <col width="14" customWidth="1" style="15" min="4" max="4"/>
+    <col width="52" customWidth="1" style="15" min="5" max="6"/>
+    <col width="52" customWidth="1" style="16" min="6" max="6"/>
     <col width="11" customWidth="1" style="15" min="7" max="7"/>
-    <col width="14" customWidth="1" style="15" min="8" max="8"/>
-    <col width="11" customWidth="1" style="15" min="9" max="9"/>
+    <col width="13" customWidth="1" style="15" min="8" max="8"/>
+    <col width="9" customWidth="1" style="15" min="9" max="9"/>
     <col width="10" customWidth="1" style="15" min="10" max="10"/>
     <col width="12" customWidth="1" style="15" min="11" max="13"/>
+    <col width="12" customWidth="1" style="16" min="12" max="12"/>
+    <col width="12" customWidth="1" style="16" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.85" customHeight="1" s="16">
@@ -5876,743 +5889,6648 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1" s="16">
+    <row r="3" s="16">
       <c r="A3" s="24">
         <f>"TASK-"&amp;TEXT(2,"000")</f>
         <v/>
       </c>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="25" t="n"/>
-      <c r="I3" s="27" t="n"/>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="25" t="n"/>
-      <c r="L3" s="28" t="n"/>
-      <c r="M3" s="28" t="n"/>
-    </row>
-    <row r="4" ht="15" customHeight="1" s="16">
+      <c r="B3" s="31" t="inlineStr">
+        <is>
+          <t>UC-001</t>
+        </is>
+      </c>
+      <c r="C3" s="31" t="inlineStr">
+        <is>
+          <t>Email + password registration</t>
+        </is>
+      </c>
+      <c r="D3" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E3" s="31" t="inlineStr">
+        <is>
+          <t>Register form on LandingView (authMode 'register') calling supabaseAuth.signUpWithPassword, with client-side Supabase auth only — the backend never issues tokens.</t>
+        </is>
+      </c>
+      <c r="F3" s="31" t="inlineStr">
+        <is>
+          <t>Given a new email, when the form is submitted, then a Supabase identity and a core.app_user row exist and the OTP screen is shown.</t>
+        </is>
+      </c>
+      <c r="G3" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H3" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I3" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J3" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K3" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L3" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M3" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="4" s="16">
       <c r="A4" s="24">
         <f>"TASK-"&amp;TEXT(3,"000")</f>
         <v/>
       </c>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="27" t="n"/>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="25" t="n"/>
-      <c r="L4" s="28" t="n"/>
-      <c r="M4" s="28" t="n"/>
-    </row>
-    <row r="5" ht="15" customHeight="1" s="16">
+      <c r="B4" s="31" t="inlineStr">
+        <is>
+          <t>UC-002</t>
+        </is>
+      </c>
+      <c r="C4" s="31" t="inlineStr">
+        <is>
+          <t>Sign-up OTP confirmation + resend guard</t>
+        </is>
+      </c>
+      <c r="D4" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E4" s="31" t="inlineStr">
+        <is>
+          <t>6-digit OTP screen wired to verifySignupOtp / resendSignupConfirmation, with resend throttled by services/emailSendGuard.ts.</t>
+        </is>
+      </c>
+      <c r="F4" s="31" t="inlineStr">
+        <is>
+          <t>Given a valid code, when it is entered, then the email is confirmed and a session starts; resend is blocked inside the guard window.</t>
+        </is>
+      </c>
+      <c r="G4" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H4" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I4" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J4" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K4" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L4" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M4" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="5" s="16">
       <c r="A5" s="24">
         <f>"TASK-"&amp;TEXT(4,"000")</f>
         <v/>
       </c>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="25" t="n"/>
-      <c r="I5" s="27" t="n"/>
-      <c r="J5" s="25" t="n"/>
-      <c r="K5" s="25" t="n"/>
-      <c r="L5" s="28" t="n"/>
-      <c r="M5" s="28" t="n"/>
-    </row>
-    <row r="6" ht="15" customHeight="1" s="16">
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>UC-003</t>
+        </is>
+      </c>
+      <c r="C5" s="31" t="inlineStr">
+        <is>
+          <t>Password sign-in with single-call profile load</t>
+        </is>
+      </c>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E5" s="31" t="inlineStr">
+        <is>
+          <t>signInWithPassword followed by one GET /me call, replacing the old multi-round-trip PostgREST reads.</t>
+        </is>
+      </c>
+      <c r="F5" s="31" t="inlineStr">
+        <is>
+          <t>Given a confirmed account, when the student signs in, then the profile snapshot loads in a single request.</t>
+        </is>
+      </c>
+      <c r="G5" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I5" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J5" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K5" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L5" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M5" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="6" s="16">
       <c r="A6" s="24">
         <f>"TASK-"&amp;TEXT(5,"000")</f>
         <v/>
       </c>
-      <c r="B6" s="25" t="n"/>
-      <c r="C6" s="25" t="n"/>
-      <c r="D6" s="25" t="n"/>
-      <c r="E6" s="25" t="n"/>
-      <c r="F6" s="25" t="n"/>
-      <c r="G6" s="25" t="n"/>
-      <c r="H6" s="25" t="n"/>
-      <c r="I6" s="27" t="n"/>
-      <c r="J6" s="25" t="n"/>
-      <c r="K6" s="25" t="n"/>
-      <c r="L6" s="28" t="n"/>
-      <c r="M6" s="28" t="n"/>
-    </row>
-    <row r="7" ht="15" customHeight="1" s="16">
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>UC-004</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="inlineStr">
+        <is>
+          <t>Passwordless email OTP sign-in</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E6" s="31" t="inlineStr">
+        <is>
+          <t>sendEmailOtp / verifyEmailOtp with otpFlow distinguishing register from login (shouldCreateUser=false on login).</t>
+        </is>
+      </c>
+      <c r="F6" s="31" t="inlineStr">
+        <is>
+          <t>Given an existing email, when the emailed code is entered, then the student is signed in without a password.</t>
+        </is>
+      </c>
+      <c r="G6" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I6" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K6" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L6" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M6" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="7" s="16">
       <c r="A7" s="24">
         <f>"TASK-"&amp;TEXT(6,"000")</f>
         <v/>
       </c>
-      <c r="B7" s="25" t="n"/>
-      <c r="C7" s="25" t="n"/>
-      <c r="D7" s="25" t="n"/>
-      <c r="E7" s="25" t="n"/>
-      <c r="F7" s="25" t="n"/>
-      <c r="G7" s="25" t="n"/>
-      <c r="H7" s="25" t="n"/>
-      <c r="I7" s="27" t="n"/>
-      <c r="J7" s="25" t="n"/>
-      <c r="K7" s="25" t="n"/>
-      <c r="L7" s="28" t="n"/>
-      <c r="M7" s="28" t="n"/>
-    </row>
-    <row r="8" ht="15" customHeight="1" s="16">
+      <c r="B7" s="31" t="inlineStr">
+        <is>
+          <t>UC-005</t>
+        </is>
+      </c>
+      <c r="C7" s="31" t="inlineStr">
+        <is>
+          <t>Mobile OTP sign-in (E.164 normalisation)</t>
+        </is>
+      </c>
+      <c r="D7" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E7" s="31" t="inlineStr">
+        <is>
+          <t>sendPhoneOtp / verifyPhoneOtp with mobile numbers normalised to E.164 before the request.</t>
+        </is>
+      </c>
+      <c r="F7" s="31" t="inlineStr">
+        <is>
+          <t>Given a valid Indian mobile number, when the SMS code is entered, then the student is signed in via the phone identity.</t>
+        </is>
+      </c>
+      <c r="G7" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H7" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I7" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K7" s="31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L7" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M7" s="33" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="8" s="16">
       <c r="A8" s="24">
         <f>"TASK-"&amp;TEXT(7,"000")</f>
         <v/>
       </c>
-      <c r="B8" s="25" t="n"/>
-      <c r="C8" s="25" t="n"/>
-      <c r="D8" s="25" t="n"/>
-      <c r="E8" s="25" t="n"/>
-      <c r="F8" s="25" t="n"/>
-      <c r="G8" s="25" t="n"/>
-      <c r="H8" s="25" t="n"/>
-      <c r="I8" s="27" t="n"/>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="25" t="n"/>
-      <c r="L8" s="28" t="n"/>
-      <c r="M8" s="28" t="n"/>
-    </row>
-    <row r="9" ht="15" customHeight="1" s="16">
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>UC-005</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="inlineStr">
+        <is>
+          <t>SMS cost guard before enabling phone OTP for real traffic</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E8" s="31" t="inlineStr">
+        <is>
+          <t>Per-number and per-IP send limits plus a spend cap, closing the per-SMS cost trap flagged in docs/FRONTEND.md sec 5.6.</t>
+        </is>
+      </c>
+      <c r="F8" s="31" t="inlineStr">
+        <is>
+          <t>Given repeated OTP requests for one number, when the limit is hit, then further sends are refused and the attempt is logged.</t>
+        </is>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H8" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I8" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K8" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L8" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M8" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="9" s="16">
       <c r="A9" s="24">
         <f>"TASK-"&amp;TEXT(8,"000")</f>
         <v/>
       </c>
-      <c r="B9" s="25" t="n"/>
-      <c r="C9" s="25" t="n"/>
-      <c r="D9" s="25" t="n"/>
-      <c r="E9" s="25" t="n"/>
-      <c r="F9" s="25" t="n"/>
-      <c r="G9" s="25" t="n"/>
-      <c r="H9" s="25" t="n"/>
-      <c r="I9" s="27" t="n"/>
-      <c r="J9" s="25" t="n"/>
-      <c r="K9" s="25" t="n"/>
-      <c r="L9" s="28" t="n"/>
-      <c r="M9" s="28" t="n"/>
-    </row>
-    <row r="10" ht="15" customHeight="1" s="16">
+      <c r="B9" s="31" t="inlineStr">
+        <is>
+          <t>UC-006</t>
+        </is>
+      </c>
+      <c r="C9" s="31" t="inlineStr">
+        <is>
+          <t>Google / LinkedIn OAuth sign-in</t>
+        </is>
+      </c>
+      <c r="D9" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E9" s="31" t="inlineStr">
+        <is>
+          <t>signInWithGoogle / signInWithLinkedIn plus the Google One Tap prompt in services/googleOneTap.ts.</t>
+        </is>
+      </c>
+      <c r="F9" s="31" t="inlineStr">
+        <is>
+          <t>Given an enabled provider, when the student completes consent, then a federated identity is linked and the session starts.</t>
+        </is>
+      </c>
+      <c r="G9" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H9" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I9" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K9" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L9" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M9" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="10" s="16">
       <c r="A10" s="24">
         <f>"TASK-"&amp;TEXT(9,"000")</f>
         <v/>
       </c>
-      <c r="B10" s="25" t="n"/>
-      <c r="C10" s="25" t="n"/>
-      <c r="D10" s="25" t="n"/>
-      <c r="E10" s="25" t="n"/>
-      <c r="F10" s="25" t="n"/>
-      <c r="G10" s="25" t="n"/>
-      <c r="H10" s="25" t="n"/>
-      <c r="I10" s="27" t="n"/>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="25" t="n"/>
-      <c r="L10" s="28" t="n"/>
-      <c r="M10" s="28" t="n"/>
-    </row>
-    <row r="11" ht="15" customHeight="1" s="16">
+      <c r="B10" s="31" t="inlineStr">
+        <is>
+          <t>UC-007</t>
+        </is>
+      </c>
+      <c r="C10" s="31" t="inlineStr">
+        <is>
+          <t>One-click demo login</t>
+        </is>
+      </c>
+      <c r="D10" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E10" s="31" t="inlineStr">
+        <is>
+          <t>services/demoSession.ts ensureDemoSession plus the shared-account demo badge in Header.tsx.</t>
+        </is>
+      </c>
+      <c r="F10" s="31" t="inlineStr">
+        <is>
+          <t>Given a visitor on the landing page, when Demo Account is clicked, then they land inside the app on sample data with the badge visible.</t>
+        </is>
+      </c>
+      <c r="G10" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H10" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I10" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K10" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L10" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M10" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="11" s="16">
       <c r="A11" s="24">
         <f>"TASK-"&amp;TEXT(10,"000")</f>
         <v/>
       </c>
-      <c r="B11" s="25" t="n"/>
-      <c r="C11" s="25" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="25" t="n"/>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="28" t="n"/>
-      <c r="M11" s="28" t="n"/>
-    </row>
-    <row r="12" ht="15" customHeight="1" s="16">
+      <c r="B11" s="31" t="inlineStr">
+        <is>
+          <t>UC-008</t>
+        </is>
+      </c>
+      <c r="C11" s="31" t="inlineStr">
+        <is>
+          <t>Demo account reset endpoint</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E11" s="31" t="inlineStr">
+        <is>
+          <t>POST /auth/demo/reset in demoController.resetDemoAccountData clearing attempts and learn-layer rows.</t>
+        </is>
+      </c>
+      <c r="F11" s="31" t="inlineStr">
+        <is>
+          <t>Given the demo account has data, when reset is called, then attempts and learn rows are cleared and the user row survives.</t>
+        </is>
+      </c>
+      <c r="G11" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H11" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I11" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K11" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L11" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M11" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="12" s="16">
       <c r="A12" s="24">
         <f>"TASK-"&amp;TEXT(11,"000")</f>
         <v/>
       </c>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="25" t="n"/>
-      <c r="H12" s="25" t="n"/>
-      <c r="I12" s="27" t="n"/>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="28" t="n"/>
-      <c r="M12" s="28" t="n"/>
-    </row>
-    <row r="13" ht="15" customHeight="1" s="16">
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>UC-009</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="inlineStr">
+        <is>
+          <t>Email availability lookup with rate limit</t>
+        </is>
+      </c>
+      <c r="D12" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E12" s="31" t="inlineStr">
+        <is>
+          <t>GET /auth/email-availability in emailAvailability.service.ts, rate-limited so it cannot be used as an enumeration oracle.</t>
+        </is>
+      </c>
+      <c r="F12" s="31" t="inlineStr">
+        <is>
+          <t>Given a registered email, when it is typed, then the UI routes to sign-in; repeated lookups from one caller are throttled.</t>
+        </is>
+      </c>
+      <c r="G12" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H12" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I12" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J12" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K12" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L12" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M12" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="13" s="16">
       <c r="A13" s="24">
         <f>"TASK-"&amp;TEXT(12,"000")</f>
         <v/>
       </c>
-      <c r="B13" s="25" t="n"/>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="25" t="n"/>
-      <c r="E13" s="25" t="n"/>
-      <c r="F13" s="25" t="n"/>
-      <c r="G13" s="25" t="n"/>
-      <c r="H13" s="25" t="n"/>
-      <c r="I13" s="27" t="n"/>
-      <c r="J13" s="25" t="n"/>
-      <c r="K13" s="25" t="n"/>
-      <c r="L13" s="28" t="n"/>
-      <c r="M13" s="28" t="n"/>
-    </row>
-    <row r="14" ht="15" customHeight="1" s="16">
+      <c r="B13" s="31" t="inlineStr">
+        <is>
+          <t>UC-010</t>
+        </is>
+      </c>
+      <c r="C13" s="31" t="inlineStr">
+        <is>
+          <t>Idle session heartbeat and expiry warning</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="E13" s="31" t="inlineStr">
+        <is>
+          <t>POST /auth/session/heartbeat with useIdleSessionGuard.ts and SessionExpiryModal warning before idle/absolute expiry.</t>
+        </is>
+      </c>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>Given an idle session near timeout, when the threshold passes, then the warning modal appears and the student can extend or end cleanly.</t>
+        </is>
+      </c>
+      <c r="G13" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H13" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="I13" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K13" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L13" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M13" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="14" s="16">
       <c r="A14" s="24">
         <f>"TASK-"&amp;TEXT(13,"000")</f>
         <v/>
       </c>
-      <c r="B14" s="25" t="n"/>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="25" t="n"/>
-      <c r="H14" s="25" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="25" t="n"/>
-      <c r="L14" s="28" t="n"/>
-      <c r="M14" s="28" t="n"/>
-    </row>
-    <row r="15" ht="15" customHeight="1" s="16">
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>UC-011</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="inlineStr">
+        <is>
+          <t>Sign out</t>
+        </is>
+      </c>
+      <c r="D14" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E14" s="31" t="inlineStr">
+        <is>
+          <t>Profile-menu sign-out calling POST /auth/session/logout and dropping cached profile state.</t>
+        </is>
+      </c>
+      <c r="F14" s="31" t="inlineStr">
+        <is>
+          <t>Given a signed-in student, when Sign Out is clicked, then the session ends and no cached profile remains.</t>
+        </is>
+      </c>
+      <c r="G14" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H14" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I14" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K14" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L14" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M14" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="15" s="16">
       <c r="A15" s="24">
         <f>"TASK-"&amp;TEXT(14,"000")</f>
         <v/>
       </c>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
-      <c r="G15" s="25" t="n"/>
-      <c r="H15" s="25" t="n"/>
-      <c r="I15" s="27" t="n"/>
-      <c r="J15" s="25" t="n"/>
-      <c r="K15" s="25" t="n"/>
-      <c r="L15" s="28" t="n"/>
-      <c r="M15" s="28" t="n"/>
-    </row>
-    <row r="16" ht="15" customHeight="1" s="16">
+      <c r="B15" s="31" t="inlineStr">
+        <is>
+          <t>UC-003</t>
+        </is>
+      </c>
+      <c r="C15" s="31" t="inlineStr">
+        <is>
+          <t>Regression pass across all six sign-in paths</t>
+        </is>
+      </c>
+      <c r="D15" s="31" t="inlineStr">
+        <is>
+          <t>QA/Testing</t>
+        </is>
+      </c>
+      <c r="E15" s="31" t="inlineStr">
+        <is>
+          <t>Exercise password, email OTP, phone OTP, Google, LinkedIn and demo sign-in end to end on desktop and mobile widths.</t>
+        </is>
+      </c>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>Given each of the six paths, when it is run against a clean account, then sign-in succeeds and GET /me returns the right profile.</t>
+        </is>
+      </c>
+      <c r="G15" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H15" s="31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I15" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K15" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L15" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M15" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="16" s="16">
       <c r="A16" s="24">
         <f>"TASK-"&amp;TEXT(15,"000")</f>
         <v/>
       </c>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="25" t="n"/>
-      <c r="I16" s="27" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="25" t="n"/>
-      <c r="L16" s="28" t="n"/>
-      <c r="M16" s="28" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1" s="16">
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>UC-012</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="inlineStr">
+        <is>
+          <t>Onboarding sync (exam, class, target year)</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E16" s="31" t="inlineStr">
+        <is>
+          <t>GET /me onboarding sync in meProfile.service.ts persisting targetExam, classLevel and targetYear on core.student_profile.</t>
+        </is>
+      </c>
+      <c r="F16" s="31" t="inlineStr">
+        <is>
+          <t>Given a new student completes onboarding, when GET /me is called, then the three fields are persisted and returned.</t>
+        </is>
+      </c>
+      <c r="G16" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H16" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I16" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K16" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L16" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M16" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="17" s="16">
       <c r="A17" s="24">
         <f>"TASK-"&amp;TEXT(16,"000")</f>
         <v/>
       </c>
-      <c r="B17" s="25" t="n"/>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
-      <c r="G17" s="25" t="n"/>
-      <c r="H17" s="25" t="n"/>
-      <c r="I17" s="27" t="n"/>
-      <c r="J17" s="25" t="n"/>
-      <c r="K17" s="25" t="n"/>
-      <c r="L17" s="28" t="n"/>
-      <c r="M17" s="28" t="n"/>
-    </row>
-    <row r="18" ht="15" customHeight="1" s="16">
+      <c r="B17" s="31" t="inlineStr">
+        <is>
+          <t>UC-013</t>
+        </is>
+      </c>
+      <c r="C17" s="31" t="inlineStr">
+        <is>
+          <t>Consolidated profile snapshot (GET /me)</t>
+        </is>
+      </c>
+      <c r="D17" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E17" s="31" t="inlineStr">
+        <is>
+          <t>getFullProfile returning identity, role, status, plan and academic details in one authoritative response.</t>
+        </is>
+      </c>
+      <c r="F17" s="31" t="inlineStr">
+        <is>
+          <t>Given a valid access token, when GET /me is called, then one response carries every field ProfileView renders.</t>
+        </is>
+      </c>
+      <c r="G17" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H17" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I17" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J17" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K17" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L17" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M17" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="18" s="16">
       <c r="A18" s="24">
         <f>"TASK-"&amp;TEXT(17,"000")</f>
         <v/>
       </c>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="n"/>
-      <c r="G18" s="25" t="n"/>
-      <c r="H18" s="25" t="n"/>
-      <c r="I18" s="27" t="n"/>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="25" t="n"/>
-      <c r="L18" s="28" t="n"/>
-      <c r="M18" s="28" t="n"/>
-    </row>
-    <row r="19" ht="15" customHeight="1" s="16">
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>UC-014</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="inlineStr">
+        <is>
+          <t>Strict self-service profile update</t>
+        </is>
+      </c>
+      <c r="D18" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E18" s="31" t="inlineStr">
+        <is>
+          <t>PATCH /me with a .strict() updateProfileSchema so forbidden fields are rejected rather than silently dropped.</t>
+        </is>
+      </c>
+      <c r="F18" s="31" t="inlineStr">
+        <is>
+          <t>Given a payload containing a non-self-editable field, when it is submitted, then the request is rejected with a field-level error.</t>
+        </is>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H18" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I18" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K18" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L18" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M18" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="19" s="16">
       <c r="A19" s="24">
         <f>"TASK-"&amp;TEXT(18,"000")</f>
         <v/>
       </c>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
-      <c r="G19" s="25" t="n"/>
-      <c r="H19" s="25" t="n"/>
-      <c r="I19" s="27" t="n"/>
-      <c r="J19" s="25" t="n"/>
-      <c r="K19" s="25" t="n"/>
-      <c r="L19" s="28" t="n"/>
-      <c r="M19" s="28" t="n"/>
-    </row>
-    <row r="20" ht="15" customHeight="1" s="16">
+      <c r="B19" s="31" t="inlineStr">
+        <is>
+          <t>UC-015</t>
+        </is>
+      </c>
+      <c r="C19" s="31" t="inlineStr">
+        <is>
+          <t>Wrap remaining Header and Dashboard strings in t() (DB-05 phase 1)</t>
+        </is>
+      </c>
+      <c r="D19" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E19" s="31" t="inlineStr">
+        <is>
+          <t>First screen-by-screen pass of the deferred i18n sweep: wrap unwrapped strings and add the missing en.json / ta.json keys for Header and Dashboard.</t>
+        </is>
+      </c>
+      <c r="F19" s="31" t="inlineStr">
+        <is>
+          <t>Given the UI language is Tamil, when Header and Dashboard are opened, then no English string remains and every key resolves.</t>
+        </is>
+      </c>
+      <c r="G19" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H19" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I19" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J19" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K19" s="31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L19" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M19" s="33" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="20" s="16">
       <c r="A20" s="24">
         <f>"TASK-"&amp;TEXT(19,"000")</f>
         <v/>
       </c>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="25" t="n"/>
-      <c r="G20" s="25" t="n"/>
-      <c r="H20" s="25" t="n"/>
-      <c r="I20" s="27" t="n"/>
-      <c r="J20" s="25" t="n"/>
-      <c r="K20" s="25" t="n"/>
-      <c r="L20" s="28" t="n"/>
-      <c r="M20" s="28" t="n"/>
-    </row>
-    <row r="21" ht="15" customHeight="1" s="16">
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>UC-015</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
+        <is>
+          <t>Tamil string-coverage sweep across remaining screens (DB-05)</t>
+        </is>
+      </c>
+      <c r="D20" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E20" s="31" t="inlineStr">
+        <is>
+          <t>Continue the sweep across the other useLanguage() consumers, then run the exit gate: click through every route in Tamil.</t>
+        </is>
+      </c>
+      <c r="F20" s="31" t="inlineStr">
+        <is>
+          <t>Given every route is visited in Tamil, when the click-through completes, then zero untranslated strings are found.</t>
+        </is>
+      </c>
+      <c r="G20" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H20" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I20" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="J20" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K20" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L20" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="M20" s="33" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="21" s="16">
       <c r="A21" s="24">
         <f>"TASK-"&amp;TEXT(20,"000")</f>
         <v/>
       </c>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="25" t="n"/>
-      <c r="G21" s="25" t="n"/>
-      <c r="H21" s="25" t="n"/>
-      <c r="I21" s="27" t="n"/>
-      <c r="J21" s="25" t="n"/>
-      <c r="K21" s="25" t="n"/>
-      <c r="L21" s="28" t="n"/>
-      <c r="M21" s="28" t="n"/>
-    </row>
-    <row r="22" ht="15" customHeight="1" s="16">
+      <c r="B21" s="31" t="inlineStr">
+        <is>
+          <t>UC-016</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="inlineStr">
+        <is>
+          <t>Light / dark theme toggle</t>
+        </is>
+      </c>
+      <c r="D21" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E21" s="31" t="inlineStr">
+        <is>
+          <t>Header.tsx toggleDarkMode with Tailwind v4 dark: variants and a persisted preference.</t>
+        </is>
+      </c>
+      <c r="F21" s="31" t="inlineStr">
+        <is>
+          <t>Given dark mode is chosen, when the app reloads, then the theme is still dark.</t>
+        </is>
+      </c>
+      <c r="G21" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H21" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I21" s="32" t="n">
+        <v>1</v>
+      </c>
+      <c r="J21" s="31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K21" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L21" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M21" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="22" s="16">
       <c r="A22" s="24">
         <f>"TASK-"&amp;TEXT(21,"000")</f>
         <v/>
       </c>
-      <c r="B22" s="25" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="25" t="n"/>
-      <c r="G22" s="25" t="n"/>
-      <c r="H22" s="25" t="n"/>
-      <c r="I22" s="27" t="n"/>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="25" t="n"/>
-      <c r="L22" s="28" t="n"/>
-      <c r="M22" s="28" t="n"/>
-    </row>
-    <row r="23" ht="15" customHeight="1" s="16">
+      <c r="B22" s="31" t="inlineStr">
+        <is>
+          <t>UC-017</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="inlineStr">
+        <is>
+          <t>Persist notification and security preferences server-side</t>
+        </is>
+      </c>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="E22" s="31" t="inlineStr">
+        <is>
+          <t>Replace Header.tsx's local useState toggles (twoFactor, dailyReminders, whatsappUpdates, emailDiagnosticReports) with a real preferences table and GET/PATCH endpoints.</t>
+        </is>
+      </c>
+      <c r="F22" s="31" t="inlineStr">
+        <is>
+          <t>Given a toggle is changed, when the app reloads on another device, then the stored value is returned by the API and rendered.</t>
+        </is>
+      </c>
+      <c r="G22" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H22" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="I22" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J22" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K22" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L22" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M22" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="23" s="16">
       <c r="A23" s="24">
         <f>"TASK-"&amp;TEXT(22,"000")</f>
         <v/>
       </c>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-      <c r="G23" s="25" t="n"/>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="27" t="n"/>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="25" t="n"/>
-      <c r="L23" s="28" t="n"/>
-      <c r="M23" s="28" t="n"/>
-    </row>
-    <row r="24" ht="15" customHeight="1" s="16">
+      <c r="B23" s="31" t="inlineStr">
+        <is>
+          <t>UC-017</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="inlineStr">
+        <is>
+          <t>Wire reminder and diagnostic delivery to stored preferences</t>
+        </is>
+      </c>
+      <c r="D23" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E23" s="31" t="inlineStr">
+        <is>
+          <t>Make the reminder, WhatsApp and diagnostic-email senders read the persisted preferences instead of firing unconditionally.</t>
+        </is>
+      </c>
+      <c r="F23" s="31" t="inlineStr">
+        <is>
+          <t>Given a student disables daily reminders, when the scheduler runs, then no reminder is sent to that student.</t>
+        </is>
+      </c>
+      <c r="G23" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H23" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I23" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J23" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K23" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L23" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="M23" s="33" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="24" s="16">
       <c r="A24" s="24">
         <f>"TASK-"&amp;TEXT(23,"000")</f>
         <v/>
       </c>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="25" t="n"/>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="25" t="n"/>
-      <c r="G24" s="25" t="n"/>
-      <c r="H24" s="25" t="n"/>
-      <c r="I24" s="27" t="n"/>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="25" t="n"/>
-      <c r="L24" s="28" t="n"/>
-      <c r="M24" s="28" t="n"/>
-    </row>
-    <row r="25" ht="15" customHeight="1" s="16">
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>UC-017</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="inlineStr">
+        <is>
+          <t>Two-factor enrolment behind the security toggle</t>
+        </is>
+      </c>
+      <c r="D24" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="E24" s="31" t="inlineStr">
+        <is>
+          <t>Enrolment, verification and recovery-code flow for the 2FA toggle that today only sets local state.</t>
+        </is>
+      </c>
+      <c r="F24" s="31" t="inlineStr">
+        <is>
+          <t>Given 2FA is enabled, when the student next signs in, then a second factor is required and recovery codes are issued once.</t>
+        </is>
+      </c>
+      <c r="G24" s="31" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H24" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="I24" s="32" t="n">
+        <v>13</v>
+      </c>
+      <c r="J24" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K24" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L24" s="33" t="n"/>
+      <c r="M24" s="33" t="n"/>
+    </row>
+    <row r="25" s="16">
       <c r="A25" s="24">
         <f>"TASK-"&amp;TEXT(24,"000")</f>
         <v/>
       </c>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="25" t="n"/>
-      <c r="G25" s="25" t="n"/>
-      <c r="H25" s="25" t="n"/>
-      <c r="I25" s="27" t="n"/>
-      <c r="J25" s="25" t="n"/>
-      <c r="K25" s="25" t="n"/>
-      <c r="L25" s="28" t="n"/>
-      <c r="M25" s="28" t="n"/>
-    </row>
-    <row r="26" ht="15" customHeight="1" s="16">
+      <c r="B25" s="31" t="inlineStr">
+        <is>
+          <t>UC-018</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="inlineStr">
+        <is>
+          <t>Catalog tree endpoint fetched once per session</t>
+        </is>
+      </c>
+      <c r="D25" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E25" s="31" t="inlineStr">
+        <is>
+          <t>GET /catalog/tree returning exam &gt; subject &gt; unit &gt; chapter &gt; topic, consumed by catalogApi.ts and fetched once in App.tsx.</t>
+        </is>
+      </c>
+      <c r="F25" s="31" t="inlineStr">
+        <is>
+          <t>Given the app loads, when the tree is fetched, then every scope picker is populated from that single response.</t>
+        </is>
+      </c>
+      <c r="G25" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H25" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I25" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K25" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L25" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M25" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="26" s="16">
       <c r="A26" s="24">
         <f>"TASK-"&amp;TEXT(25,"000")</f>
         <v/>
       </c>
-      <c r="B26" s="25" t="n"/>
-      <c r="C26" s="25" t="n"/>
-      <c r="D26" s="25" t="n"/>
-      <c r="E26" s="25" t="n"/>
-      <c r="F26" s="25" t="n"/>
-      <c r="G26" s="25" t="n"/>
-      <c r="H26" s="25" t="n"/>
-      <c r="I26" s="27" t="n"/>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="25" t="n"/>
-      <c r="L26" s="28" t="n"/>
-      <c r="M26" s="28" t="n"/>
-    </row>
-    <row r="27" ht="15" customHeight="1" s="16">
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>UC-019</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="inlineStr">
+        <is>
+          <t>NEET course area and syllabus browsing</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E26" s="31" t="inlineStr">
+        <is>
+          <t>CourseAreaView / CoursesView over data/syllabusData.ts, with the route into unit-scoped practice.</t>
+        </is>
+      </c>
+      <c r="F26" s="31" t="inlineStr">
+        <is>
+          <t>Given the NEET tab, when a unit is opened, then its chapters render and Build Test starts a scoped attempt.</t>
+        </is>
+      </c>
+      <c r="G26" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H26" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I26" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J26" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K26" s="31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L26" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M26" s="33" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="27" s="16">
       <c r="A27" s="24">
         <f>"TASK-"&amp;TEXT(26,"000")</f>
         <v/>
       </c>
-      <c r="B27" s="25" t="n"/>
-      <c r="C27" s="25" t="n"/>
-      <c r="D27" s="25" t="n"/>
-      <c r="E27" s="25" t="n"/>
-      <c r="F27" s="25" t="n"/>
-      <c r="G27" s="25" t="n"/>
-      <c r="H27" s="25" t="n"/>
-      <c r="I27" s="27" t="n"/>
-      <c r="J27" s="25" t="n"/>
-      <c r="K27" s="25" t="n"/>
-      <c r="L27" s="28" t="n"/>
-      <c r="M27" s="28" t="n"/>
-    </row>
-    <row r="28" ht="15" customHeight="1" s="16">
+      <c r="B27" s="31" t="inlineStr">
+        <is>
+          <t>UC-019</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="inlineStr">
+        <is>
+          <t>Replace empty JEE tabs with an explicit coming-soon state</t>
+        </is>
+      </c>
+      <c r="D27" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E27" s="31" t="inlineStr">
+        <is>
+          <t>The JEE Mains and Advanced tabs are deliberate placeholders today and render blank; give them an honest empty state.</t>
+        </is>
+      </c>
+      <c r="F27" s="31" t="inlineStr">
+        <is>
+          <t>Given the JEE tab is opened, when no syllabus exists, then a clear coming-soon panel is shown instead of an empty page.</t>
+        </is>
+      </c>
+      <c r="G27" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H27" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I27" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J27" s="31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K27" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L27" s="33" t="n">
+        <v>46315</v>
+      </c>
+      <c r="M27" s="33" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="28" s="16">
       <c r="A28" s="24">
         <f>"TASK-"&amp;TEXT(27,"000")</f>
         <v/>
       </c>
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="25" t="n"/>
-      <c r="D28" s="25" t="n"/>
-      <c r="E28" s="25" t="n"/>
-      <c r="F28" s="25" t="n"/>
-      <c r="G28" s="25" t="n"/>
-      <c r="H28" s="25" t="n"/>
-      <c r="I28" s="27" t="n"/>
-      <c r="J28" s="25" t="n"/>
-      <c r="K28" s="25" t="n"/>
-      <c r="L28" s="28" t="n"/>
-      <c r="M28" s="28" t="n"/>
-    </row>
-    <row r="29" ht="15" customHeight="1" s="16">
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>UC-020</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="inlineStr">
+        <is>
+          <t>Unit study material preview and download</t>
+        </is>
+      </c>
+      <c r="D28" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="E28" s="31" t="inlineStr">
+        <is>
+          <t>unitMaterialController redirect plus the frontend content-type check that stops a Google sign-in page being saved as a fake PDF.</t>
+        </is>
+      </c>
+      <c r="F28" s="31" t="inlineStr">
+        <is>
+          <t>Given a shared Drive file, when download is clicked, then a valid file is saved; given an unshared one, a single clear message is shown.</t>
+        </is>
+      </c>
+      <c r="G28" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H28" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="I28" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K28" s="31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L28" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M28" s="33" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="29" s="16">
       <c r="A29" s="24">
         <f>"TASK-"&amp;TEXT(28,"000")</f>
         <v/>
       </c>
-      <c r="B29" s="25" t="n"/>
-      <c r="C29" s="25" t="n"/>
-      <c r="D29" s="25" t="n"/>
-      <c r="E29" s="25" t="n"/>
-      <c r="F29" s="25" t="n"/>
-      <c r="G29" s="25" t="n"/>
-      <c r="H29" s="25" t="n"/>
-      <c r="I29" s="27" t="n"/>
-      <c r="J29" s="25" t="n"/>
-      <c r="K29" s="25" t="n"/>
-      <c r="L29" s="28" t="n"/>
-      <c r="M29" s="28" t="n"/>
-    </row>
-    <row r="30" ht="15" customHeight="1" s="16">
+      <c r="B29" s="31" t="inlineStr">
+        <is>
+          <t>UC-020</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="inlineStr">
+        <is>
+          <t>Re-verify Drive material access after sharing is fixed (DB-06)</t>
+        </is>
+      </c>
+      <c r="D29" s="31" t="inlineStr">
+        <is>
+          <t>QA/Testing</t>
+        </is>
+      </c>
+      <c r="E29" s="31" t="inlineStr">
+        <is>
+          <t>All 82 learn.unit_material rows point at Drive files that are not link-shared. Blocked on the Drive owner changing sharing, then re-run db/scripts/check-drive-material-access.ts.</t>
+        </is>
+      </c>
+      <c r="F29" s="31" t="inlineStr">
+        <is>
+          <t>Given sharing is set to Anyone with the link, when the script runs, then all 82 files return the file rather than a sign-in wall.</t>
+        </is>
+      </c>
+      <c r="G29" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H29" s="31" t="inlineStr">
+        <is>
+          <t>Content Ops</t>
+        </is>
+      </c>
+      <c r="I29" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K29" s="31" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="L29" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M29" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="30" s="16">
       <c r="A30" s="24">
         <f>"TASK-"&amp;TEXT(29,"000")</f>
         <v/>
       </c>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="25" t="n"/>
-      <c r="E30" s="25" t="n"/>
-      <c r="F30" s="25" t="n"/>
-      <c r="G30" s="25" t="n"/>
-      <c r="H30" s="25" t="n"/>
-      <c r="I30" s="27" t="n"/>
-      <c r="J30" s="25" t="n"/>
-      <c r="K30" s="25" t="n"/>
-      <c r="L30" s="28" t="n"/>
-      <c r="M30" s="28" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1" s="16">
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>UC-021</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="inlineStr">
+        <is>
+          <t>Expose the resource library book list through an API</t>
+        </is>
+      </c>
+      <c r="D30" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E30" s="31" t="inlineStr">
+        <is>
+          <t>Load db/books/I20_23_Resource_Library_Book_List_REAL.json behind a read route; today the data exists with no endpoint.</t>
+        </is>
+      </c>
+      <c r="F30" s="31" t="inlineStr">
+        <is>
+          <t>Given the endpoint is called, when a subject filter is passed, then the matching books are returned with their metadata.</t>
+        </is>
+      </c>
+      <c r="G30" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H30" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I30" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J30" s="31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K30" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L30" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="M30" s="33" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="31" s="16">
       <c r="A31" s="24">
         <f>"TASK-"&amp;TEXT(30,"000")</f>
         <v/>
       </c>
-      <c r="B31" s="25" t="n"/>
-      <c r="C31" s="25" t="n"/>
-      <c r="D31" s="25" t="n"/>
-      <c r="E31" s="25" t="n"/>
-      <c r="F31" s="25" t="n"/>
-      <c r="G31" s="25" t="n"/>
-      <c r="H31" s="25" t="n"/>
-      <c r="I31" s="27" t="n"/>
-      <c r="J31" s="25" t="n"/>
-      <c r="K31" s="25" t="n"/>
-      <c r="L31" s="28" t="n"/>
-      <c r="M31" s="28" t="n"/>
-    </row>
-    <row r="32" ht="15" customHeight="1" s="16">
+      <c r="B31" s="31" t="inlineStr">
+        <is>
+          <t>UC-021</t>
+        </is>
+      </c>
+      <c r="C31" s="31" t="inlineStr">
+        <is>
+          <t>Resource library browse screen</t>
+        </is>
+      </c>
+      <c r="D31" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E31" s="31" t="inlineStr">
+        <is>
+          <t>First UI over the book list: browse by subject, open a book's details.</t>
+        </is>
+      </c>
+      <c r="F31" s="31" t="inlineStr">
+        <is>
+          <t>Given the library is opened, when a subject is chosen, then its recommended books render from the API.</t>
+        </is>
+      </c>
+      <c r="G31" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H31" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I31" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J31" s="31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K31" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L31" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="M31" s="33" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="32" s="16">
       <c r="A32" s="24">
         <f>"TASK-"&amp;TEXT(31,"000")</f>
         <v/>
       </c>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="25" t="n"/>
-      <c r="D32" s="25" t="n"/>
-      <c r="E32" s="25" t="n"/>
-      <c r="F32" s="25" t="n"/>
-      <c r="G32" s="25" t="n"/>
-      <c r="H32" s="25" t="n"/>
-      <c r="I32" s="27" t="n"/>
-      <c r="J32" s="25" t="n"/>
-      <c r="K32" s="25" t="n"/>
-      <c r="L32" s="28" t="n"/>
-      <c r="M32" s="28" t="n"/>
-    </row>
-    <row r="33" ht="15" customHeight="1" s="16">
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>UC-022</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
+        <is>
+          <t>Subject / chapter / topic practice configurator</t>
+        </is>
+      </c>
+      <c r="D32" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="E32" s="31" t="inlineStr">
+        <is>
+          <t>TestListView configuration plus sessionController.createSession, a discriminated union over the four test modes.</t>
+        </is>
+      </c>
+      <c r="F32" s="31" t="inlineStr">
+        <is>
+          <t>Given a scope and count, when Start is pressed, then a published assess.test and a live attempt exist.</t>
+        </is>
+      </c>
+      <c r="G32" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H32" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="I32" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J32" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K32" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L32" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M32" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="33" s="16">
       <c r="A33" s="24">
         <f>"TASK-"&amp;TEXT(32,"000")</f>
         <v/>
       </c>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="25" t="n"/>
-      <c r="D33" s="25" t="n"/>
-      <c r="E33" s="25" t="n"/>
-      <c r="F33" s="25" t="n"/>
-      <c r="G33" s="25" t="n"/>
-      <c r="H33" s="25" t="n"/>
-      <c r="I33" s="27" t="n"/>
-      <c r="J33" s="25" t="n"/>
-      <c r="K33" s="25" t="n"/>
-      <c r="L33" s="28" t="n"/>
-      <c r="M33" s="28" t="n"/>
-    </row>
-    <row r="34" ht="15" customHeight="1" s="16">
+      <c r="B33" s="31" t="inlineStr">
+        <is>
+          <t>UC-025</t>
+        </is>
+      </c>
+      <c r="C33" s="31" t="inlineStr">
+        <is>
+          <t>Image-only practice mode</t>
+        </is>
+      </c>
+      <c r="D33" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E33" s="31" t="inlineStr">
+        <is>
+          <t>sessionController mode 'image-practice' with asset-resolver and QuestionImage handling the diagram items.</t>
+        </is>
+      </c>
+      <c r="F33" s="31" t="inlineStr">
+        <is>
+          <t>Given the image mode, when the attempt is built, then every question carries an image and a short pool fails clearly.</t>
+        </is>
+      </c>
+      <c r="G33" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H33" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I33" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K33" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L33" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M33" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="34" s="16">
       <c r="A34" s="24">
         <f>"TASK-"&amp;TEXT(33,"000")</f>
         <v/>
       </c>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="25" t="n"/>
-      <c r="D34" s="25" t="n"/>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="25" t="n"/>
-      <c r="G34" s="25" t="n"/>
-      <c r="H34" s="25" t="n"/>
-      <c r="I34" s="27" t="n"/>
-      <c r="J34" s="25" t="n"/>
-      <c r="K34" s="25" t="n"/>
-      <c r="L34" s="28" t="n"/>
-      <c r="M34" s="28" t="n"/>
-    </row>
-    <row r="35" ht="15" customHeight="1" s="16">
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>UC-026</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="inlineStr">
+        <is>
+          <t>Full NEET mock with practice-first gate</t>
+        </is>
+      </c>
+      <c r="D34" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E34" s="31" t="inlineStr">
+        <is>
+          <t>sessionController mode 'full-mock' plus the hasCompletedPracticeTest gate before a full paper can start.</t>
+        </is>
+      </c>
+      <c r="F34" s="31" t="inlineStr">
+        <is>
+          <t>Given no completed practice test, when Mock Test is clicked, then the gate explains why; otherwise a full sectioned attempt starts.</t>
+        </is>
+      </c>
+      <c r="G34" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H34" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I34" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J34" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K34" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L34" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M34" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="35" s="16">
       <c r="A35" s="24">
         <f>"TASK-"&amp;TEXT(34,"000")</f>
         <v/>
       </c>
-      <c r="B35" s="25" t="n"/>
-      <c r="C35" s="25" t="n"/>
-      <c r="D35" s="25" t="n"/>
-      <c r="E35" s="25" t="n"/>
-      <c r="F35" s="25" t="n"/>
-      <c r="G35" s="25" t="n"/>
-      <c r="H35" s="25" t="n"/>
-      <c r="I35" s="27" t="n"/>
-      <c r="J35" s="25" t="n"/>
-      <c r="K35" s="25" t="n"/>
-      <c r="L35" s="28" t="n"/>
-      <c r="M35" s="28" t="n"/>
-    </row>
-    <row r="36" ht="15" customHeight="1" s="16">
+      <c r="B35" s="31" t="inlineStr">
+        <is>
+          <t>UC-027</t>
+        </is>
+      </c>
+      <c r="C35" s="31" t="inlineStr">
+        <is>
+          <t>Custom multi-scope paper</t>
+        </is>
+      </c>
+      <c r="D35" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E35" s="31" t="inlineStr">
+        <is>
+          <t>Mode 'custom' with TestListView.distributeCount spreading the requested total across the chosen buckets.</t>
+        </is>
+      </c>
+      <c r="F35" s="31" t="inlineStr">
+        <is>
+          <t>Given several scopes and a total, when the test starts, then the counts are distributed and every scope is represented.</t>
+        </is>
+      </c>
+      <c r="G35" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H35" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I35" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K35" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L35" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M35" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="36" s="16">
       <c r="A36" s="24">
         <f>"TASK-"&amp;TEXT(35,"000")</f>
         <v/>
       </c>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="25" t="n"/>
-      <c r="D36" s="25" t="n"/>
-      <c r="E36" s="25" t="n"/>
-      <c r="F36" s="25" t="n"/>
-      <c r="G36" s="25" t="n"/>
-      <c r="H36" s="25" t="n"/>
-      <c r="I36" s="27" t="n"/>
-      <c r="J36" s="25" t="n"/>
-      <c r="K36" s="25" t="n"/>
-      <c r="L36" s="28" t="n"/>
-      <c r="M36" s="28" t="n"/>
-    </row>
-    <row r="37" ht="15" customHeight="1" s="16">
+      <c r="B36" s="31" t="inlineStr">
+        <is>
+          <t>UC-028</t>
+        </is>
+      </c>
+      <c r="C36" s="31" t="inlineStr">
+        <is>
+          <t>Launch a test from a course unit or plan goal</t>
+        </is>
+      </c>
+      <c r="D36" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E36" s="31" t="inlineStr">
+        <is>
+          <t>CoursesView / StudyPlanView name-match handoff into the test configurator.</t>
+        </is>
+      </c>
+      <c r="F36" s="31" t="inlineStr">
+        <is>
+          <t>Given a unit or goal, when Build Test is clicked, then the attempt starts pre-scoped to it.</t>
+        </is>
+      </c>
+      <c r="G36" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H36" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I36" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J36" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K36" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L36" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M36" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="37" s="16">
       <c r="A37" s="24">
         <f>"TASK-"&amp;TEXT(36,"000")</f>
         <v/>
       </c>
-      <c r="B37" s="25" t="n"/>
-      <c r="C37" s="25" t="n"/>
-      <c r="D37" s="25" t="n"/>
-      <c r="E37" s="25" t="n"/>
-      <c r="F37" s="25" t="n"/>
-      <c r="G37" s="25" t="n"/>
-      <c r="H37" s="25" t="n"/>
-      <c r="I37" s="27" t="n"/>
-      <c r="J37" s="25" t="n"/>
-      <c r="K37" s="25" t="n"/>
-      <c r="L37" s="28" t="n"/>
-      <c r="M37" s="28" t="n"/>
-    </row>
-    <row r="38" ht="15" customHeight="1" s="16">
+      <c r="B37" s="31" t="inlineStr">
+        <is>
+          <t>UC-028</t>
+        </is>
+      </c>
+      <c r="C37" s="31" t="inlineStr">
+        <is>
+          <t>Replace the name-match handoff with catalog ids</t>
+        </is>
+      </c>
+      <c r="D37" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E37" s="31" t="inlineStr">
+        <is>
+          <t>Local syllabus strings are matched to catalog nodes by name today; carry the real uuid through the handoff instead.</t>
+        </is>
+      </c>
+      <c r="F37" s="31" t="inlineStr">
+        <is>
+          <t>Given a unit whose title differs from the catalog label, when Build Test is clicked, then the correct scope is still selected.</t>
+        </is>
+      </c>
+      <c r="G37" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H37" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I37" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J37" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K37" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L37" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="M37" s="33" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="38" s="16">
       <c r="A38" s="24">
         <f>"TASK-"&amp;TEXT(37,"000")</f>
         <v/>
       </c>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="25" t="n"/>
-      <c r="D38" s="25" t="n"/>
-      <c r="E38" s="25" t="n"/>
-      <c r="F38" s="25" t="n"/>
-      <c r="G38" s="25" t="n"/>
-      <c r="H38" s="25" t="n"/>
-      <c r="I38" s="27" t="n"/>
-      <c r="J38" s="25" t="n"/>
-      <c r="K38" s="25" t="n"/>
-      <c r="L38" s="28" t="n"/>
-      <c r="M38" s="28" t="n"/>
-    </row>
-    <row r="39" ht="15" customHeight="1" s="16">
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>UC-029</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
+        <is>
+          <t>Practice test definition API</t>
+        </is>
+      </c>
+      <c r="D38" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E38" s="31" t="inlineStr">
+        <is>
+          <t>POST /assess/tests/practice with the allowlist derived from TEST_TYPE_CONFIG so it cannot drift from the engine.</t>
+        </is>
+      </c>
+      <c r="F38" s="31" t="inlineStr">
+        <is>
+          <t>Given a valid exam and scope, when the endpoint is called, then a published test is created that any attempt flow can start.</t>
+        </is>
+      </c>
+      <c r="G38" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H38" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I38" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J38" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K38" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L38" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M38" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="39" s="16">
       <c r="A39" s="24">
         <f>"TASK-"&amp;TEXT(38,"000")</f>
         <v/>
       </c>
-      <c r="B39" s="25" t="n"/>
-      <c r="C39" s="25" t="n"/>
-      <c r="D39" s="25" t="n"/>
-      <c r="E39" s="25" t="n"/>
-      <c r="F39" s="25" t="n"/>
-      <c r="G39" s="25" t="n"/>
-      <c r="H39" s="25" t="n"/>
-      <c r="I39" s="27" t="n"/>
-      <c r="J39" s="25" t="n"/>
-      <c r="K39" s="25" t="n"/>
-      <c r="L39" s="28" t="n"/>
-      <c r="M39" s="28" t="n"/>
-    </row>
-    <row r="40" ht="15" customHeight="1" s="16">
+      <c r="B39" s="31" t="inlineStr">
+        <is>
+          <t>UC-023</t>
+        </is>
+      </c>
+      <c r="C39" s="31" t="inlineStr">
+        <is>
+          <t>Live question availability while configuring</t>
+        </is>
+      </c>
+      <c r="D39" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="E39" s="31" t="inlineStr">
+        <is>
+          <t>POST /assess/availability debounced from the configurator, surfaced by QuestionAvailabilityBanner.</t>
+        </is>
+      </c>
+      <c r="F39" s="31" t="inlineStr">
+        <is>
+          <t>Given a config change, when the pool is short, then the banner warns before Start rather than after.</t>
+        </is>
+      </c>
+      <c r="G39" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H39" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="I39" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J39" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K39" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L39" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M39" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="40" s="16">
       <c r="A40" s="24">
         <f>"TASK-"&amp;TEXT(39,"000")</f>
         <v/>
       </c>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="25" t="n"/>
-      <c r="D40" s="25" t="n"/>
-      <c r="E40" s="25" t="n"/>
-      <c r="F40" s="25" t="n"/>
-      <c r="G40" s="25" t="n"/>
-      <c r="H40" s="25" t="n"/>
-      <c r="I40" s="27" t="n"/>
-      <c r="J40" s="25" t="n"/>
-      <c r="K40" s="25" t="n"/>
-      <c r="L40" s="28" t="n"/>
-      <c r="M40" s="28" t="n"/>
-    </row>
-    <row r="41" ht="15" customHeight="1" s="16">
+      <c r="B40" s="31" t="inlineStr">
+        <is>
+          <t>UC-024</t>
+        </is>
+      </c>
+      <c r="C40" s="31" t="inlineStr">
+        <is>
+          <t>Insufficient question pool dialog</t>
+        </is>
+      </c>
+      <c r="D40" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E40" s="31" t="inlineStr">
+        <is>
+          <t>InsufficientQuestionsDialog covering the POOL-01..POOL-15 boundary cases in docs/TEST-CASES.md.</t>
+        </is>
+      </c>
+      <c r="F40" s="31" t="inlineStr">
+        <is>
+          <t>Given a scope that is short, when the student starts, then no attempt row is created and the shortfall is spelled out.</t>
+        </is>
+      </c>
+      <c r="G40" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H40" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I40" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J40" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K40" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L40" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M40" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="41" s="16">
       <c r="A41" s="24">
         <f>"TASK-"&amp;TEXT(40,"000")</f>
         <v/>
       </c>
-      <c r="B41" s="25" t="n"/>
-      <c r="C41" s="25" t="n"/>
-      <c r="D41" s="25" t="n"/>
-      <c r="E41" s="25" t="n"/>
-      <c r="F41" s="25" t="n"/>
-      <c r="G41" s="25" t="n"/>
-      <c r="H41" s="25" t="n"/>
-      <c r="I41" s="27" t="n"/>
-      <c r="J41" s="25" t="n"/>
-      <c r="K41" s="25" t="n"/>
-      <c r="L41" s="28" t="n"/>
-      <c r="M41" s="28" t="n"/>
-    </row>
-    <row r="42" ht="15" customHeight="1" s="16">
+      <c r="B41" s="31" t="inlineStr">
+        <is>
+          <t>UC-030</t>
+        </is>
+      </c>
+      <c r="C41" s="31" t="inlineStr">
+        <is>
+          <t>Pre-test system check</t>
+        </is>
+      </c>
+      <c r="D41" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E41" s="31" t="inlineStr">
+        <is>
+          <t>SystemCheckView covering browser compatibility, network, display and memory before the exam screen.</t>
+        </is>
+      </c>
+      <c r="F41" s="31" t="inlineStr">
+        <is>
+          <t>Given a failing check, when the student proceeds, then the specific failure is named and the entry is gated.</t>
+        </is>
+      </c>
+      <c r="G41" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H41" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I41" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J41" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K41" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L41" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M41" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="42" s="16">
       <c r="A42" s="24">
         <f>"TASK-"&amp;TEXT(41,"000")</f>
         <v/>
       </c>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="25" t="n"/>
-      <c r="D42" s="25" t="n"/>
-      <c r="E42" s="25" t="n"/>
-      <c r="F42" s="25" t="n"/>
-      <c r="G42" s="25" t="n"/>
-      <c r="H42" s="25" t="n"/>
-      <c r="I42" s="27" t="n"/>
-      <c r="J42" s="25" t="n"/>
-      <c r="K42" s="25" t="n"/>
-      <c r="L42" s="28" t="n"/>
-      <c r="M42" s="28" t="n"/>
+      <c r="B42" s="31" t="inlineStr">
+        <is>
+          <t>UC-031</t>
+        </is>
+      </c>
+      <c r="C42" s="31" t="inlineStr">
+        <is>
+          <t>Exam lobby with countdown and recycling disclosure</t>
+        </is>
+      </c>
+      <c r="D42" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E42" s="31" t="inlineStr">
+        <is>
+          <t>LobbyView with the 30-second settle-in and the repeated-question disclosure required by docs/no-repeat-questions-fix.md Phase 5.</t>
+        </is>
+      </c>
+      <c r="F42" s="31" t="inlineStr">
+        <is>
+          <t>Given a lobby entry, when the countdown ends, then the test opens and the disclosure has been shown.</t>
+        </is>
+      </c>
+      <c r="G42" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H42" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I42" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J42" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K42" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L42" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M42" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="43" s="16">
+      <c r="A43" s="24">
+        <f>"TASK-"&amp;TEXT(42,"000")</f>
+        <v/>
+      </c>
+      <c r="B43" s="31" t="inlineStr">
+        <is>
+          <t>UC-032</t>
+        </is>
+      </c>
+      <c r="C43" s="31" t="inlineStr">
+        <is>
+          <t>One active attempt per student</t>
+        </is>
+      </c>
+      <c r="D43" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E43" s="31" t="inlineStr">
+        <is>
+          <t>attempt-flow.startAttempt refusing a second concurrent attempt with ACTIVE_ATTEMPT_EXISTS wired into the resume prompt.</t>
+        </is>
+      </c>
+      <c r="F43" s="31" t="inlineStr">
+        <is>
+          <t>Given an in-progress attempt, when another start is requested, then it is refused and the student is pointed at the live attempt.</t>
+        </is>
+      </c>
+      <c r="G43" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H43" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I43" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J43" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K43" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L43" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M43" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="44" s="16">
+      <c r="A44" s="24">
+        <f>"TASK-"&amp;TEXT(43,"000")</f>
+        <v/>
+      </c>
+      <c r="B44" s="31" t="inlineStr">
+        <is>
+          <t>UC-032</t>
+        </is>
+      </c>
+      <c r="C44" s="31" t="inlineStr">
+        <is>
+          <t>Thread the transaction client through assembleForAttempt (DB-01)</t>
+        </is>
+      </c>
+      <c r="D44" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E44" s="31" t="inlineStr">
+        <is>
+          <t>startAttempt calls assembleForAttempt inside its own transaction while assembly uses bare pool.query — four concurrent BLUEPRINT starts can deadlock the 4-connection pool, the same bug already fixed in loadSectionSchemes.</t>
+        </is>
+      </c>
+      <c r="F44" s="31" t="inlineStr">
+        <is>
+          <t>Given four or more simultaneous starts on one test, when they run, then all complete and no backend sits idle in transaction.</t>
+        </is>
+      </c>
+      <c r="G44" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H44" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I44" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J44" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K44" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L44" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M44" s="33" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="45" s="16">
+      <c r="A45" s="24">
+        <f>"TASK-"&amp;TEXT(44,"000")</f>
+        <v/>
+      </c>
+      <c r="B45" s="31" t="inlineStr">
+        <is>
+          <t>UC-032</t>
+        </is>
+      </c>
+      <c r="C45" s="31" t="inlineStr">
+        <is>
+          <t>Concurrent-start load test for the assembly path</t>
+        </is>
+      </c>
+      <c r="D45" s="31" t="inlineStr">
+        <is>
+          <t>QA/Testing</t>
+        </is>
+      </c>
+      <c r="E45" s="31" t="inlineStr">
+        <is>
+          <t>Extend concurrent-shared-pool.test.ts to cover startAttempt at 8+ real concurrent callers once DB-01 lands.</t>
+        </is>
+      </c>
+      <c r="F45" s="31" t="inlineStr">
+        <is>
+          <t>Given eight concurrent starts, when the test runs, then every attempt gets its full distinct question set with no deadlock.</t>
+        </is>
+      </c>
+      <c r="G45" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H45" s="31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I45" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J45" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K45" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L45" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M45" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="46" s="16">
+      <c r="A46" s="24">
+        <f>"TASK-"&amp;TEXT(45,"000")</f>
+        <v/>
+      </c>
+      <c r="B46" s="31" t="inlineStr">
+        <is>
+          <t>UC-033</t>
+        </is>
+      </c>
+      <c r="C46" s="31" t="inlineStr">
+        <is>
+          <t>Autosaved responses</t>
+        </is>
+      </c>
+      <c r="D46" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E46" s="31" t="inlineStr">
+        <is>
+          <t>saveResponse / batchSaveResponses behind requireAttemptOwnership, keeping the latest answer per question.</t>
+        </is>
+      </c>
+      <c r="F46" s="31" t="inlineStr">
+        <is>
+          <t>Given an answer change, when the network drops before submit, then the last saved answer survives a reload.</t>
+        </is>
+      </c>
+      <c r="G46" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H46" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I46" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J46" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K46" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L46" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M46" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="47" s="16">
+      <c r="A47" s="24">
+        <f>"TASK-"&amp;TEXT(46,"000")</f>
+        <v/>
+      </c>
+      <c r="B47" s="31" t="inlineStr">
+        <is>
+          <t>UC-034</t>
+        </is>
+      </c>
+      <c r="C47" s="31" t="inlineStr">
+        <is>
+          <t>Question palette and mark-for-review</t>
+        </is>
+      </c>
+      <c r="D47" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E47" s="31" t="inlineStr">
+        <is>
+          <t>TestTakingView orderQuestions() ordering by section and sequence, with an off-canvas palette on mobile.</t>
+        </is>
+      </c>
+      <c r="F47" s="31" t="inlineStr">
+        <is>
+          <t>Given any question state, when the palette is opened, then every question is reachable and its state is visible at 390px and up.</t>
+        </is>
+      </c>
+      <c r="G47" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H47" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I47" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J47" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K47" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L47" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M47" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="48" s="16">
+      <c r="A48" s="24">
+        <f>"TASK-"&amp;TEXT(47,"000")</f>
+        <v/>
+      </c>
+      <c r="B48" s="31" t="inlineStr">
+        <is>
+          <t>UC-034</t>
+        </is>
+      </c>
+      <c r="C48" s="31" t="inlineStr">
+        <is>
+          <t>Trace the stray 'Case #12' label near the stem (DB-07)</t>
+        </is>
+      </c>
+      <c r="D48" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E48" s="31" t="inlineStr">
+        <is>
+          <t>No published stem matches the reported pattern, so the label is almost certainly a counter or index leaking into the stem container — inspect the render path.</t>
+        </is>
+      </c>
+      <c r="F48" s="31" t="inlineStr">
+        <is>
+          <t>Given the reported paper, when the question renders, then no counter label appears inside or adjacent to the stem text.</t>
+        </is>
+      </c>
+      <c r="G48" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H48" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I48" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J48" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K48" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L48" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M48" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="49" s="16">
+      <c r="A49" s="24">
+        <f>"TASK-"&amp;TEXT(48,"000")</f>
+        <v/>
+      </c>
+      <c r="B49" s="31" t="inlineStr">
+        <is>
+          <t>UC-035</t>
+        </is>
+      </c>
+      <c r="C49" s="31" t="inlineStr">
+        <is>
+          <t>Countdown timer and auto-submit at zero</t>
+        </is>
+      </c>
+      <c r="D49" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E49" s="31" t="inlineStr">
+        <is>
+          <t>TestTakingView timer with warning states and onCompleteTest firing the same submit path as the manual button (LOCK-18).</t>
+        </is>
+      </c>
+      <c r="F49" s="31" t="inlineStr">
+        <is>
+          <t>Given the timer reaches zero, when auto-submit runs, then the attempt is scored and no further input is accepted.</t>
+        </is>
+      </c>
+      <c r="G49" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H49" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I49" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J49" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K49" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L49" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M49" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="50" s="16">
+      <c r="A50" s="24">
+        <f>"TASK-"&amp;TEXT(49,"000")</f>
+        <v/>
+      </c>
+      <c r="B50" s="31" t="inlineStr">
+        <is>
+          <t>UC-036</t>
+        </is>
+      </c>
+      <c r="C50" s="31" t="inlineStr">
+        <is>
+          <t>Exam lockdown: close out the LOCK-01..LOCK-20 list</t>
+        </is>
+      </c>
+      <c r="D50" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E50" s="31" t="inlineStr">
+        <is>
+          <t>Back/forward interception, refresh confirmation, copy and context-menu suppression and the remaining automatable lockdown cases in docs/TEST-CASES.md Bucket 3.</t>
+        </is>
+      </c>
+      <c r="F50" s="31" t="inlineStr">
+        <is>
+          <t>Given each automatable LOCK case, when the suite runs, then it passes; the manual-only cases are listed with evidence.</t>
+        </is>
+      </c>
+      <c r="G50" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H50" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I50" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J50" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K50" s="31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L50" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M50" s="33" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="51" s="16">
+      <c r="A51" s="24">
+        <f>"TASK-"&amp;TEXT(50,"000")</f>
+        <v/>
+      </c>
+      <c r="B51" s="31" t="inlineStr">
+        <is>
+          <t>UC-036</t>
+        </is>
+      </c>
+      <c r="C51" s="31" t="inlineStr">
+        <is>
+          <t>Manual lockdown pass on mobile</t>
+        </is>
+      </c>
+      <c r="D51" s="31" t="inlineStr">
+        <is>
+          <t>QA/Testing</t>
+        </is>
+      </c>
+      <c r="E51" s="31" t="inlineStr">
+        <is>
+          <t>Run the manual-only LOCK mobile variants on real devices, recording evidence per case.</t>
+        </is>
+      </c>
+      <c r="F51" s="31" t="inlineStr">
+        <is>
+          <t>Given each mobile LOCK case, when it is exercised on a real device, then the observed behaviour is recorded pass or fail.</t>
+        </is>
+      </c>
+      <c r="G51" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H51" s="31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I51" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K51" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L51" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M51" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="52" s="16">
+      <c r="A52" s="24">
+        <f>"TASK-"&amp;TEXT(51,"000")</f>
+        <v/>
+      </c>
+      <c r="B52" s="31" t="inlineStr">
+        <is>
+          <t>UC-037</t>
+        </is>
+      </c>
+      <c r="C52" s="31" t="inlineStr">
+        <is>
+          <t>Attempt integrity event trail</t>
+        </is>
+      </c>
+      <c r="D52" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E52" s="31" t="inlineStr">
+        <is>
+          <t>postEvent / getEvents recording blur, focus and fullscreen-exit as an append-only trail per attempt (LOCK-06).</t>
+        </is>
+      </c>
+      <c r="F52" s="31" t="inlineStr">
+        <is>
+          <t>Given a tab switch mid-attempt, when the attempt is inspected, then the event is present with its timestamp.</t>
+        </is>
+      </c>
+      <c r="G52" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H52" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I52" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J52" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K52" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L52" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M52" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="53" s="16">
+      <c r="A53" s="24">
+        <f>"TASK-"&amp;TEXT(52,"000")</f>
+        <v/>
+      </c>
+      <c r="B53" s="31" t="inlineStr">
+        <is>
+          <t>UC-038</t>
+        </is>
+      </c>
+      <c r="C53" s="31" t="inlineStr">
+        <is>
+          <t>Pause an attempt with the clock frozen</t>
+        </is>
+      </c>
+      <c r="D53" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E53" s="31" t="inlineStr">
+        <is>
+          <t>attempt-flow.pauseAttempt with envelope referenceNowMs freezing the clock so viewing progress costs no time.</t>
+        </is>
+      </c>
+      <c r="F53" s="31" t="inlineStr">
+        <is>
+          <t>Given a pause, when the attempt is reopened later, then the remaining time is exactly what it was at pause.</t>
+        </is>
+      </c>
+      <c r="G53" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H53" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I53" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J53" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K53" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L53" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M53" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="54" s="16">
+      <c r="A54" s="24">
+        <f>"TASK-"&amp;TEXT(53,"000")</f>
+        <v/>
+      </c>
+      <c r="B54" s="31" t="inlineStr">
+        <is>
+          <t>UC-039</t>
+        </is>
+      </c>
+      <c r="C54" s="31" t="inlineStr">
+        <is>
+          <t>Resume a paused attempt</t>
+        </is>
+      </c>
+      <c r="D54" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E54" s="31" t="inlineStr">
+        <is>
+          <t>PausedAttemptPanel with Resume as the primary action and Submit demoted to secondary.</t>
+        </is>
+      </c>
+      <c r="F54" s="31" t="inlineStr">
+        <is>
+          <t>Given a paused attempt, when Resume is clicked, then the same paper and remaining time return in progress.</t>
+        </is>
+      </c>
+      <c r="G54" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H54" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I54" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K54" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L54" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M54" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="55" s="16">
+      <c r="A55" s="24">
+        <f>"TASK-"&amp;TEXT(54,"000")</f>
+        <v/>
+      </c>
+      <c r="B55" s="31" t="inlineStr">
+        <is>
+          <t>UC-040</t>
+        </is>
+      </c>
+      <c r="C55" s="31" t="inlineStr">
+        <is>
+          <t>Recover an in-progress attempt after a refresh or crash</t>
+        </is>
+      </c>
+      <c r="D55" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E55" s="31" t="inlineStr">
+        <is>
+          <t>useResumableAttempt restoring the live attempt on load (LOCK-05, BUG-03/BUG-06).</t>
+        </is>
+      </c>
+      <c r="F55" s="31" t="inlineStr">
+        <is>
+          <t>Given a mid-test reload, when the app boots, then the student lands back on the same paper with saved answers intact.</t>
+        </is>
+      </c>
+      <c r="G55" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H55" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I55" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J55" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K55" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L55" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M55" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="56" s="16">
+      <c r="A56" s="24">
+        <f>"TASK-"&amp;TEXT(55,"000")</f>
+        <v/>
+      </c>
+      <c r="B56" s="31" t="inlineStr">
+        <is>
+          <t>UC-042</t>
+        </is>
+      </c>
+      <c r="C56" s="31" t="inlineStr">
+        <is>
+          <t>No repeated questions inside or across attempts</t>
+        </is>
+      </c>
+      <c r="D56" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E56" s="31" t="inlineStr">
+        <is>
+          <t>content_fp-protected blueprint assembly plus the exposure ledger, covered by REP-01..REP-25.</t>
+        </is>
+      </c>
+      <c r="F56" s="31" t="inlineStr">
+        <is>
+          <t>Given repeated attempts on one scope, when papers are assembled, then no question repeats inside an attempt and repeats across attempts stay inside the policy window.</t>
+        </is>
+      </c>
+      <c r="G56" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H56" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I56" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J56" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K56" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L56" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M56" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="57" s="16">
+      <c r="A57" s="24">
+        <f>"TASK-"&amp;TEXT(56,"000")</f>
+        <v/>
+      </c>
+      <c r="B57" s="31" t="inlineStr">
+        <is>
+          <t>UC-042</t>
+        </is>
+      </c>
+      <c r="C57" s="31" t="inlineStr">
+        <is>
+          <t>Decide hard vs soft anti-repeat window (REP-13)</t>
+        </is>
+      </c>
+      <c r="D57" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E57" s="31" t="inlineStr">
+        <is>
+          <t>REP-13 records an open policy question: a hard block on recently-seen items versus a soft de-prioritisation when the pool is thin.</t>
+        </is>
+      </c>
+      <c r="F57" s="31" t="inlineStr">
+        <is>
+          <t>Given a thin pool, when the policy is applied, then the chosen behaviour is documented, implemented and covered by a test.</t>
+        </is>
+      </c>
+      <c r="G57" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H57" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I57" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J57" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K57" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L57" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="M57" s="33" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="58" s="16">
+      <c r="A58" s="24">
+        <f>"TASK-"&amp;TEXT(57,"000")</f>
+        <v/>
+      </c>
+      <c r="B58" s="31" t="inlineStr">
+        <is>
+          <t>UC-041</t>
+        </is>
+      </c>
+      <c r="C58" s="31" t="inlineStr">
+        <is>
+          <t>Server-side scoring on submit</t>
+        </is>
+      </c>
+      <c r="D58" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E58" s="31" t="inlineStr">
+        <is>
+          <t>attempt-flow.submitAttempt with db/assess/scoring, and EvaluatingView showing real progress rather than a simulation.</t>
+        </is>
+      </c>
+      <c r="F58" s="31" t="inlineStr">
+        <is>
+          <t>Given a submitted attempt, when scoring completes, then marks come only from the server and match the marking scheme.</t>
+        </is>
+      </c>
+      <c r="G58" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H58" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I58" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J58" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K58" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L58" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M58" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="59" s="16">
+      <c r="A59" s="24">
+        <f>"TASK-"&amp;TEXT(58,"000")</f>
+        <v/>
+      </c>
+      <c r="B59" s="31" t="inlineStr">
+        <is>
+          <t>UC-043</t>
+        </is>
+      </c>
+      <c r="C59" s="31" t="inlineStr">
+        <is>
+          <t>Scorecard immediately after submit</t>
+        </is>
+      </c>
+      <c r="D59" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E59" s="31" t="inlineStr">
+        <is>
+          <t>getScorecard with DashboardView formatMarks rendering the result as soon as scoring returns.</t>
+        </is>
+      </c>
+      <c r="F59" s="31" t="inlineStr">
+        <is>
+          <t>Given a completed attempt, when scoring finishes, then the scorecard renders with score, accuracy and time.</t>
+        </is>
+      </c>
+      <c r="G59" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H59" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I59" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J59" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K59" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L59" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M59" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="60" s="16">
+      <c r="A60" s="24">
+        <f>"TASK-"&amp;TEXT(59,"000")</f>
+        <v/>
+      </c>
+      <c r="B60" s="31" t="inlineStr">
+        <is>
+          <t>UC-044</t>
+        </is>
+      </c>
+      <c r="C60" s="31" t="inlineStr">
+        <is>
+          <t>Results history</t>
+        </is>
+      </c>
+      <c r="D60" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E60" s="31" t="inlineStr">
+        <is>
+          <t>MyResultsView over listOwnAttempts with search and filters.</t>
+        </is>
+      </c>
+      <c r="F60" s="31" t="inlineStr">
+        <is>
+          <t>Given past attempts, when My Results is opened, then the server list renders with per-attempt entry points.</t>
+        </is>
+      </c>
+      <c r="G60" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H60" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I60" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J60" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K60" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L60" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M60" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="61" s="16">
+      <c r="A61" s="24">
+        <f>"TASK-"&amp;TEXT(60,"000")</f>
+        <v/>
+      </c>
+      <c r="B61" s="31" t="inlineStr">
+        <is>
+          <t>UC-044</t>
+        </is>
+      </c>
+      <c r="C61" s="31" t="inlineStr">
+        <is>
+          <t>Replace the ephemeral attempts array with server data (DB-03)</t>
+        </is>
+      </c>
+      <c r="D61" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E61" s="31" t="inlineStr">
+        <is>
+          <t>App.tsx's client-only attempts state still backs TestListView's recent-attempts strip and the daily-reminder check, so both go stale after a fresh login.</t>
+        </is>
+      </c>
+      <c r="F61" s="31" t="inlineStr">
+        <is>
+          <t>Given a fresh login on a new device, when the dashboard and Tests screens load, then both read real server history.</t>
+        </is>
+      </c>
+      <c r="G61" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H61" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I61" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J61" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K61" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L61" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M61" s="33" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="62" s="16">
+      <c r="A62" s="24">
+        <f>"TASK-"&amp;TEXT(61,"000")</f>
+        <v/>
+      </c>
+      <c r="B62" s="31" t="inlineStr">
+        <is>
+          <t>UC-045</t>
+        </is>
+      </c>
+      <c r="C62" s="31" t="inlineStr">
+        <is>
+          <t>Question-by-question attempt review</t>
+        </is>
+      </c>
+      <c r="D62" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E62" s="31" t="inlineStr">
+        <is>
+          <t>AttemptReviewView showing the student answer, correct answer, explanation and time per question.</t>
+        </is>
+      </c>
+      <c r="F62" s="31" t="inlineStr">
+        <is>
+          <t>Given a scored attempt, when review is opened, then every question shows both answers and time spent.</t>
+        </is>
+      </c>
+      <c r="G62" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H62" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I62" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J62" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K62" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L62" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M62" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="63" s="16">
+      <c r="A63" s="24">
+        <f>"TASK-"&amp;TEXT(62,"000")</f>
+        <v/>
+      </c>
+      <c r="B63" s="31" t="inlineStr">
+        <is>
+          <t>UC-046</t>
+        </is>
+      </c>
+      <c r="C63" s="31" t="inlineStr">
+        <is>
+          <t>IRT ability estimate</t>
+        </is>
+      </c>
+      <c r="D63" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E63" s="31" t="inlineStr">
+        <is>
+          <t>getIrtReportHandler with IrtSection rendering the ability estimate alongside the raw score.</t>
+        </is>
+      </c>
+      <c r="F63" s="31" t="inlineStr">
+        <is>
+          <t>Given a scored attempt, when the report is opened, then the ability estimate and its confidence band are shown.</t>
+        </is>
+      </c>
+      <c r="G63" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H63" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I63" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J63" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K63" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L63" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M63" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="64" s="16">
+      <c r="A64" s="24">
+        <f>"TASK-"&amp;TEXT(63,"000")</f>
+        <v/>
+      </c>
+      <c r="B64" s="31" t="inlineStr">
+        <is>
+          <t>UC-047</t>
+        </is>
+      </c>
+      <c r="C64" s="31" t="inlineStr">
+        <is>
+          <t>Cohort comparison</t>
+        </is>
+      </c>
+      <c r="D64" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E64" s="31" t="inlineStr">
+        <is>
+          <t>getCohortComparisonHandler placing the student's score against the cohort distribution.</t>
+        </is>
+      </c>
+      <c r="F64" s="31" t="inlineStr">
+        <is>
+          <t>Given enough cohort data, when the result is opened, then percentile and cohort average are shown.</t>
+        </is>
+      </c>
+      <c r="G64" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H64" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I64" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J64" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K64" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L64" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M64" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="65" s="16">
+      <c r="A65" s="24">
+        <f>"TASK-"&amp;TEXT(64,"000")</f>
+        <v/>
+      </c>
+      <c r="B65" s="31" t="inlineStr">
+        <is>
+          <t>UC-049</t>
+        </is>
+      </c>
+      <c r="C65" s="31" t="inlineStr">
+        <is>
+          <t>Branded PDF report export</t>
+        </is>
+      </c>
+      <c r="D65" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E65" s="31" t="inlineStr">
+        <is>
+          <t>services/pdfExport.ts with ReportBrandHeader and ReportSummary, lazily loaded so recharts and jsPDF stay out of the initial bundle.</t>
+        </is>
+      </c>
+      <c r="F65" s="31" t="inlineStr">
+        <is>
+          <t>Given a report, when Download PDF is used, then a branded PDF is produced and the initial bundle is unchanged.</t>
+        </is>
+      </c>
+      <c r="G65" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H65" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I65" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J65" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K65" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L65" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M65" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="66" s="16">
+      <c r="A66" s="24">
+        <f>"TASK-"&amp;TEXT(65,"000")</f>
+        <v/>
+      </c>
+      <c r="B66" s="31" t="inlineStr">
+        <is>
+          <t>UC-050</t>
+        </is>
+      </c>
+      <c r="C66" s="31" t="inlineStr">
+        <is>
+          <t>Share a scorecard</t>
+        </is>
+      </c>
+      <c r="D66" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E66" s="31" t="inlineStr">
+        <is>
+          <t>services/shareScorecard.ts with idle / working / done / failed states on the dashboard control.</t>
+        </is>
+      </c>
+      <c r="F66" s="31" t="inlineStr">
+        <is>
+          <t>Given a scorecard, when Share is used, then the share completes or fails with an explicit state, never silently.</t>
+        </is>
+      </c>
+      <c r="G66" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H66" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I66" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" s="31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K66" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L66" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M66" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="67" s="16">
+      <c r="A67" s="24">
+        <f>"TASK-"&amp;TEXT(66,"000")</f>
+        <v/>
+      </c>
+      <c r="B67" s="31" t="inlineStr">
+        <is>
+          <t>UC-048</t>
+        </is>
+      </c>
+      <c r="C67" s="31" t="inlineStr">
+        <is>
+          <t>Performance analytics dashboard</t>
+        </is>
+      </c>
+      <c r="D67" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="E67" s="31" t="inlineStr">
+        <is>
+          <t>AnalyticsView with useDashboardAnalytics over analyticsController.getDashboard, covering trends and weak areas.</t>
+        </is>
+      </c>
+      <c r="F67" s="31" t="inlineStr">
+        <is>
+          <t>Given several attempts, when Analytics is opened, then trend, subject split and weak areas render from one server call.</t>
+        </is>
+      </c>
+      <c r="G67" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H67" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="I67" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J67" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K67" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L67" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M67" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="68" s="16">
+      <c r="A68" s="24">
+        <f>"TASK-"&amp;TEXT(67,"000")</f>
+        <v/>
+      </c>
+      <c r="B68" s="31" t="inlineStr">
+        <is>
+          <t>UC-048</t>
+        </is>
+      </c>
+      <c r="C68" s="31" t="inlineStr">
+        <is>
+          <t>Subject-level drill-down in analytics</t>
+        </is>
+      </c>
+      <c r="D68" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E68" s="31" t="inlineStr">
+        <is>
+          <t>Let a student open a subject from the analytics summary and see chapter-level accuracy behind it.</t>
+        </is>
+      </c>
+      <c r="F68" s="31" t="inlineStr">
+        <is>
+          <t>Given a subject tile, when it is opened, then chapter-level accuracy and attempt counts render for that subject.</t>
+        </is>
+      </c>
+      <c r="G68" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H68" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I68" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J68" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K68" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L68" s="33" t="n">
+        <v>46315</v>
+      </c>
+      <c r="M68" s="33" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="69" s="16">
+      <c r="A69" s="24">
+        <f>"TASK-"&amp;TEXT(68,"000")</f>
+        <v/>
+      </c>
+      <c r="B69" s="31" t="inlineStr">
+        <is>
+          <t>UC-051</t>
+        </is>
+      </c>
+      <c r="C69" s="31" t="inlineStr">
+        <is>
+          <t>Create and save a study plan</t>
+        </is>
+      </c>
+      <c r="D69" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E69" s="31" t="inlineStr">
+        <is>
+          <t>studyPlanFlowController with 'me' and 'reset' registered before the generic CRUD router (BUG-19).</t>
+        </is>
+      </c>
+      <c r="F69" s="31" t="inlineStr">
+        <is>
+          <t>Given a target date, when the plan is created, then it is persisted and returned by GET /study-plans/me.</t>
+        </is>
+      </c>
+      <c r="G69" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H69" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I69" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J69" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K69" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L69" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M69" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="70" s="16">
+      <c r="A70" s="24">
+        <f>"TASK-"&amp;TEXT(69,"000")</f>
+        <v/>
+      </c>
+      <c r="B70" s="31" t="inlineStr">
+        <is>
+          <t>UC-052</t>
+        </is>
+      </c>
+      <c r="C70" s="31" t="inlineStr">
+        <is>
+          <t>Study plan goal management</t>
+        </is>
+      </c>
+      <c r="D70" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E70" s="31" t="inlineStr">
+        <is>
+          <t>Add, edit, reorder and delete goals with requirePlanOwnership resolving ownership once per request.</t>
+        </is>
+      </c>
+      <c r="F70" s="31" t="inlineStr">
+        <is>
+          <t>Given a plan, when goals are reordered or deleted, then the change persists and another student's plan is untouchable.</t>
+        </is>
+      </c>
+      <c r="G70" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H70" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I70" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J70" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K70" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L70" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M70" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="71" s="16">
+      <c r="A71" s="24">
+        <f>"TASK-"&amp;TEXT(70,"000")</f>
+        <v/>
+      </c>
+      <c r="B71" s="31" t="inlineStr">
+        <is>
+          <t>UC-053</t>
+        </is>
+      </c>
+      <c r="C71" s="31" t="inlineStr">
+        <is>
+          <t>Plan task completion tracking</t>
+        </is>
+      </c>
+      <c r="D71" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E71" s="31" t="inlineStr">
+        <is>
+          <t>learnFlowController getPlanTasks / patchPlanTaskStatus.</t>
+        </is>
+      </c>
+      <c r="F71" s="31" t="inlineStr">
+        <is>
+          <t>Given a plan task, when it is ticked, then the status persists and plan progress recomputes.</t>
+        </is>
+      </c>
+      <c r="G71" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H71" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I71" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J71" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K71" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L71" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M71" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="72" s="16">
+      <c r="A72" s="24">
+        <f>"TASK-"&amp;TEXT(71,"000")</f>
+        <v/>
+      </c>
+      <c r="B72" s="31" t="inlineStr">
+        <is>
+          <t>UC-054</t>
+        </is>
+      </c>
+      <c r="C72" s="31" t="inlineStr">
+        <is>
+          <t>Custom study tasks</t>
+        </is>
+      </c>
+      <c r="D72" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E72" s="31" t="inlineStr">
+        <is>
+          <t>learn.routes /custom-tasks backed by real tables (BUG-20/21/22 replaced the localStorage and missing-table paths).</t>
+        </is>
+      </c>
+      <c r="F72" s="31" t="inlineStr">
+        <is>
+          <t>Given a custom task, when it is created, then it survives a reload and belongs only to its owner.</t>
+        </is>
+      </c>
+      <c r="G72" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H72" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I72" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J72" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K72" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L72" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M72" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="73" s="16">
+      <c r="A73" s="24">
+        <f>"TASK-"&amp;TEXT(72,"000")</f>
+        <v/>
+      </c>
+      <c r="B73" s="31" t="inlineStr">
+        <is>
+          <t>UC-055</t>
+        </is>
+      </c>
+      <c r="C73" s="31" t="inlineStr">
+        <is>
+          <t>Personal revision notes</t>
+        </is>
+      </c>
+      <c r="D73" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="E73" s="31" t="inlineStr">
+        <is>
+          <t>learn.routes /revision-notes with services/revisionNotesApi.ts.</t>
+        </is>
+      </c>
+      <c r="F73" s="31" t="inlineStr">
+        <is>
+          <t>Given a note against a chapter, when it is saved, then it is returned on the next visit for that student only.</t>
+        </is>
+      </c>
+      <c r="G73" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H73" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="I73" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J73" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K73" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L73" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M73" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="74" s="16">
+      <c r="A74" s="24">
+        <f>"TASK-"&amp;TEXT(73,"000")</f>
+        <v/>
+      </c>
+      <c r="B74" s="31" t="inlineStr">
+        <is>
+          <t>UC-056</t>
+        </is>
+      </c>
+      <c r="C74" s="31" t="inlineStr">
+        <is>
+          <t>Daily flashcard review</t>
+        </is>
+      </c>
+      <c r="D74" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E74" s="31" t="inlineStr">
+        <is>
+          <t>DailyFlashcard with getFlashcardReviews / postFlashcardReview behind requireDeckOwnership.</t>
+        </is>
+      </c>
+      <c r="F74" s="31" t="inlineStr">
+        <is>
+          <t>Given a due card, when it is reviewed, then the review is recorded and the next due card is served.</t>
+        </is>
+      </c>
+      <c r="G74" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H74" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I74" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J74" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K74" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L74" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M74" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="75" s="16">
+      <c r="A75" s="24">
+        <f>"TASK-"&amp;TEXT(74,"000")</f>
+        <v/>
+      </c>
+      <c r="B75" s="31" t="inlineStr">
+        <is>
+          <t>UC-057</t>
+        </is>
+      </c>
+      <c r="C75" s="31" t="inlineStr">
+        <is>
+          <t>Focus sessions and study streak</t>
+        </is>
+      </c>
+      <c r="D75" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E75" s="31" t="inlineStr">
+        <is>
+          <t>FocusMode and PomodoroTimer over pomodoroSessionsListRouter, with plain-language copy after the BUG-29 wording sweep.</t>
+        </is>
+      </c>
+      <c r="F75" s="31" t="inlineStr">
+        <is>
+          <t>Given a completed focus session, when it is logged, then the streak updates and the copy contains no technical vocabulary.</t>
+        </is>
+      </c>
+      <c r="G75" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H75" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I75" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J75" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K75" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L75" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M75" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="76" s="16">
+      <c r="A76" s="24">
+        <f>"TASK-"&amp;TEXT(75,"000")</f>
+        <v/>
+      </c>
+      <c r="B76" s="31" t="inlineStr">
+        <is>
+          <t>UC-060</t>
+        </is>
+      </c>
+      <c r="C76" s="31" t="inlineStr">
+        <is>
+          <t>Auto-log wrong answers into the error log</t>
+        </is>
+      </c>
+      <c r="D76" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E76" s="31" t="inlineStr">
+        <is>
+          <t>Populate learn.error_log on submit so the mistake notebook has content; the CRUD route exists but nothing writes to it from the attempt flow.</t>
+        </is>
+      </c>
+      <c r="F76" s="31" t="inlineStr">
+        <is>
+          <t>Given a submitted attempt with wrong answers, when scoring completes, then one error-log row exists per wrong question.</t>
+        </is>
+      </c>
+      <c r="G76" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H76" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I76" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J76" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K76" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L76" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M76" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="77" s="16">
+      <c r="A77" s="24">
+        <f>"TASK-"&amp;TEXT(76,"000")</f>
+        <v/>
+      </c>
+      <c r="B77" s="31" t="inlineStr">
+        <is>
+          <t>UC-060</t>
+        </is>
+      </c>
+      <c r="C77" s="31" t="inlineStr">
+        <is>
+          <t>Mistake notebook screen</t>
+        </is>
+      </c>
+      <c r="D77" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E77" s="31" t="inlineStr">
+        <is>
+          <t>First UI over learn.routes /error-log — no frontend screen calls it today.</t>
+        </is>
+      </c>
+      <c r="F77" s="31" t="inlineStr">
+        <is>
+          <t>Given logged mistakes, when the notebook is opened, then they are listed by subject with a route back into the question.</t>
+        </is>
+      </c>
+      <c r="G77" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H77" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I77" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J77" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K77" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L77" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M77" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="78" s="16">
+      <c r="A78" s="24">
+        <f>"TASK-"&amp;TEXT(77,"000")</f>
+        <v/>
+      </c>
+      <c r="B78" s="31" t="inlineStr">
+        <is>
+          <t>UC-061</t>
+        </is>
+      </c>
+      <c r="C78" s="31" t="inlineStr">
+        <is>
+          <t>Compute and persist topic mastery on submit</t>
+        </is>
+      </c>
+      <c r="D78" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E78" s="31" t="inlineStr">
+        <is>
+          <t>Write learn.topic_mastery from attempt results instead of deriving weak areas only inside the analytics dashboard.</t>
+        </is>
+      </c>
+      <c r="F78" s="31" t="inlineStr">
+        <is>
+          <t>Given a submitted attempt, when scoring completes, then per-topic mastery rows are updated for that student.</t>
+        </is>
+      </c>
+      <c r="G78" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H78" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I78" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J78" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K78" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L78" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="M78" s="33" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="79" s="16">
+      <c r="A79" s="24">
+        <f>"TASK-"&amp;TEXT(78,"000")</f>
+        <v/>
+      </c>
+      <c r="B79" s="31" t="inlineStr">
+        <is>
+          <t>UC-061</t>
+        </is>
+      </c>
+      <c r="C79" s="31" t="inlineStr">
+        <is>
+          <t>Topic mastery screen</t>
+        </is>
+      </c>
+      <c r="D79" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E79" s="31" t="inlineStr">
+        <is>
+          <t>UI over learn.routes /topic-mastery showing per-topic scores; backend only today.</t>
+        </is>
+      </c>
+      <c r="F79" s="31" t="inlineStr">
+        <is>
+          <t>Given mastery rows, when the screen is opened, then topics are ranked with safe and at-risk bands.</t>
+        </is>
+      </c>
+      <c r="G79" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H79" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I79" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J79" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K79" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L79" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="M79" s="33" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="80" s="16">
+      <c r="A80" s="24">
+        <f>"TASK-"&amp;TEXT(79,"000")</f>
+        <v/>
+      </c>
+      <c r="B80" s="31" t="inlineStr">
+        <is>
+          <t>UC-058</t>
+        </is>
+      </c>
+      <c r="C80" s="31" t="inlineStr">
+        <is>
+          <t>In-app notification centre</t>
+        </is>
+      </c>
+      <c r="D80" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E80" s="31" t="inlineStr">
+        <is>
+          <t>NotificationBell over notificationsListRouter including clear-all (P0-5).</t>
+        </is>
+      </c>
+      <c r="F80" s="31" t="inlineStr">
+        <is>
+          <t>Given unread notifications, when the bell is opened, then they are listed and clear-all empties the list server-side.</t>
+        </is>
+      </c>
+      <c r="G80" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H80" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I80" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J80" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K80" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L80" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M80" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="81" s="16">
+      <c r="A81" s="24">
+        <f>"TASK-"&amp;TEXT(80,"000")</f>
+        <v/>
+      </c>
+      <c r="B81" s="31" t="inlineStr">
+        <is>
+          <t>UC-059</t>
+        </is>
+      </c>
+      <c r="C81" s="31" t="inlineStr">
+        <is>
+          <t>Base the daily reminder on server attempt data (DB-03)</t>
+        </is>
+      </c>
+      <c r="D81" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E81" s="31" t="inlineStr">
+        <is>
+          <t>DailyReminderModal's 'did they test today' check still reads App.tsx's ephemeral attempts array, so it misfires after a fresh login.</t>
+        </is>
+      </c>
+      <c r="F81" s="31" t="inlineStr">
+        <is>
+          <t>Given a student who tested today on another device, when the app loads, then no reminder is shown.</t>
+        </is>
+      </c>
+      <c r="G81" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H81" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I81" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J81" s="31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K81" s="31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L81" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M81" s="33" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="82" s="16">
+      <c r="A82" s="24">
+        <f>"TASK-"&amp;TEXT(81,"000")</f>
+        <v/>
+      </c>
+      <c r="B82" s="31" t="inlineStr">
+        <is>
+          <t>UC-062</t>
+        </is>
+      </c>
+      <c r="C82" s="31" t="inlineStr">
+        <is>
+          <t>Fill in the placeholder admin tabs</t>
+        </is>
+      </c>
+      <c r="D82" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E82" s="31" t="inlineStr">
+        <is>
+          <t>AdminView ships the shell and tabs (Overview/Students/Content/Analytics/Settings) with several panels still placeholders.</t>
+        </is>
+      </c>
+      <c r="F82" s="31" t="inlineStr">
+        <is>
+          <t>Given each admin tab, when it is opened, then it renders real data or an explicit empty state — no placeholder panels remain.</t>
+        </is>
+      </c>
+      <c r="G82" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H82" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I82" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J82" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K82" s="31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L82" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M82" s="33" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="83" s="16">
+      <c r="A83" s="24">
+        <f>"TASK-"&amp;TEXT(82,"000")</f>
+        <v/>
+      </c>
+      <c r="B83" s="31" t="inlineStr">
+        <is>
+          <t>UC-062</t>
+        </is>
+      </c>
+      <c r="C83" s="31" t="inlineStr">
+        <is>
+          <t>Wire the admin overview to GET /admin/stats</t>
+        </is>
+      </c>
+      <c r="D83" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="E83" s="31" t="inlineStr">
+        <is>
+          <t>Render the platform counts behind requirePermission('admin:stats') in the Overview tab.</t>
+        </is>
+      </c>
+      <c r="F83" s="31" t="inlineStr">
+        <is>
+          <t>Given an admin, when Overview is opened, then live user, attempt and content counts render; a non-admin is refused.</t>
+        </is>
+      </c>
+      <c r="G83" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H83" s="31" t="inlineStr">
+        <is>
+          <t>Full-stack</t>
+        </is>
+      </c>
+      <c r="I83" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J83" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K83" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L83" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M83" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="84" s="16">
+      <c r="A84" s="24">
+        <f>"TASK-"&amp;TEXT(83,"000")</f>
+        <v/>
+      </c>
+      <c r="B84" s="31" t="inlineStr">
+        <is>
+          <t>UC-063</t>
+        </is>
+      </c>
+      <c r="C84" s="31" t="inlineStr">
+        <is>
+          <t>User invitations</t>
+        </is>
+      </c>
+      <c r="D84" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E84" s="31" t="inlineStr">
+        <is>
+          <t>admin.routes invitation endpoints using the service-role key.</t>
+        </is>
+      </c>
+      <c r="F84" s="31" t="inlineStr">
+        <is>
+          <t>Given an invited email, when the invite is sent, then the invitee can complete sign-up against that invitation only.</t>
+        </is>
+      </c>
+      <c r="G84" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H84" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I84" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J84" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K84" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L84" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M84" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="85" s="16">
+      <c r="A85" s="24">
+        <f>"TASK-"&amp;TEXT(84,"000")</f>
+        <v/>
+      </c>
+      <c r="B85" s="31" t="inlineStr">
+        <is>
+          <t>UC-064</t>
+        </is>
+      </c>
+      <c r="C85" s="31" t="inlineStr">
+        <is>
+          <t>User search and record correction</t>
+        </is>
+      </c>
+      <c r="D85" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E85" s="31" t="inlineStr">
+        <is>
+          <t>userManageGated routes over adminUser.service.ts.</t>
+        </is>
+      </c>
+      <c r="F85" s="31" t="inlineStr">
+        <is>
+          <t>Given a support request, when an admin searches and edits a user, then the change is persisted and audited.</t>
+        </is>
+      </c>
+      <c r="G85" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H85" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I85" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J85" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K85" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L85" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M85" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="86" s="16">
+      <c r="A86" s="24">
+        <f>"TASK-"&amp;TEXT(85,"000")</f>
+        <v/>
+      </c>
+      <c r="B86" s="31" t="inlineStr">
+        <is>
+          <t>UC-065</t>
+        </is>
+      </c>
+      <c r="C86" s="31" t="inlineStr">
+        <is>
+          <t>Account status transitions</t>
+        </is>
+      </c>
+      <c r="D86" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E86" s="31" t="inlineStr">
+        <is>
+          <t>transitionStatusSchema for suspend, reactivate and delete; DELETE /me is gated behind user-manage permission plus recent OTP re-authentication (BUG-27).</t>
+        </is>
+      </c>
+      <c r="F86" s="31" t="inlineStr">
+        <is>
+          <t>Given a suspended account, when the user signs in, then access is refused; self-service deletion is not reachable without re-auth.</t>
+        </is>
+      </c>
+      <c r="G86" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H86" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I86" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J86" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K86" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L86" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M86" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="87" s="16">
+      <c r="A87" s="24">
+        <f>"TASK-"&amp;TEXT(86,"000")</f>
+        <v/>
+      </c>
+      <c r="B87" s="31" t="inlineStr">
+        <is>
+          <t>UC-066</t>
+        </is>
+      </c>
+      <c r="C87" s="31" t="inlineStr">
+        <is>
+          <t>Role grant and revoke</t>
+        </is>
+      </c>
+      <c r="D87" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E87" s="31" t="inlineStr">
+        <is>
+          <t>admin.routes role endpoints enforced by middleware/requirePermission.ts.</t>
+        </is>
+      </c>
+      <c r="F87" s="31" t="inlineStr">
+        <is>
+          <t>Given a revoked role, when the user calls a route that needed it, then the call is refused immediately.</t>
+        </is>
+      </c>
+      <c r="G87" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H87" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I87" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J87" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K87" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L87" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M87" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="88" s="16">
+      <c r="A88" s="24">
+        <f>"TASK-"&amp;TEXT(87,"000")</f>
+        <v/>
+      </c>
+      <c r="B88" s="31" t="inlineStr">
+        <is>
+          <t>UC-067</t>
+        </is>
+      </c>
+      <c r="C88" s="31" t="inlineStr">
+        <is>
+          <t>Force sign-out and force password reset</t>
+        </is>
+      </c>
+      <c r="D88" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E88" s="31" t="inlineStr">
+        <is>
+          <t>admin.routes force-sign-out / force-password-reset for compromised accounts.</t>
+        </is>
+      </c>
+      <c r="F88" s="31" t="inlineStr">
+        <is>
+          <t>Given a forced sign-out, when the user's existing session is used, then it is rejected and re-authentication is required.</t>
+        </is>
+      </c>
+      <c r="G88" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H88" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I88" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J88" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K88" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L88" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M88" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="89" s="16">
+      <c r="A89" s="24">
+        <f>"TASK-"&amp;TEXT(88,"000")</f>
+        <v/>
+      </c>
+      <c r="B89" s="31" t="inlineStr">
+        <is>
+          <t>UC-068</t>
+        </is>
+      </c>
+      <c r="C89" s="31" t="inlineStr">
+        <is>
+          <t>Submit a question for review</t>
+        </is>
+      </c>
+      <c r="D89" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E89" s="31" t="inlineStr">
+        <is>
+          <t>content.routes submit path over db/content/lifecycle.ts.</t>
+        </is>
+      </c>
+      <c r="F89" s="31" t="inlineStr">
+        <is>
+          <t>Given a draft question, when it is submitted, then its state moves to under-review and the transition is recorded.</t>
+        </is>
+      </c>
+      <c r="G89" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H89" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I89" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J89" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K89" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L89" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M89" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="90" s="16">
+      <c r="A90" s="24">
+        <f>"TASK-"&amp;TEXT(89,"000")</f>
+        <v/>
+      </c>
+      <c r="B90" s="31" t="inlineStr">
+        <is>
+          <t>UC-069</t>
+        </is>
+      </c>
+      <c r="C90" s="31" t="inlineStr">
+        <is>
+          <t>Review decision (approve or send back)</t>
+        </is>
+      </c>
+      <c r="D90" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E90" s="31" t="inlineStr">
+        <is>
+          <t>review-decision behind requirePermission('content:review_decide').</t>
+        </is>
+      </c>
+      <c r="F90" s="31" t="inlineStr">
+        <is>
+          <t>Given a question under review, when a decision is recorded, then the state and reviewer note are stored atomically.</t>
+        </is>
+      </c>
+      <c r="G90" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H90" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I90" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J90" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K90" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L90" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M90" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="91" s="16">
+      <c r="A91" s="24">
+        <f>"TASK-"&amp;TEXT(90,"000")</f>
+        <v/>
+      </c>
+      <c r="B91" s="31" t="inlineStr">
+        <is>
+          <t>UC-070</t>
+        </is>
+      </c>
+      <c r="C91" s="31" t="inlineStr">
+        <is>
+          <t>Publish and retire questions</t>
+        </is>
+      </c>
+      <c r="D91" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E91" s="31" t="inlineStr">
+        <is>
+          <t>content.routes publish/retire; POOL-14 confirms draft and retired items never count as available.</t>
+        </is>
+      </c>
+      <c r="F91" s="31" t="inlineStr">
+        <is>
+          <t>Given a retired question, when availability is computed, then it is excluded from every pool.</t>
+        </is>
+      </c>
+      <c r="G91" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H91" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I91" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J91" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K91" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L91" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M91" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="92" s="16">
+      <c r="A92" s="24">
+        <f>"TASK-"&amp;TEXT(91,"000")</f>
+        <v/>
+      </c>
+      <c r="B92" s="31" t="inlineStr">
+        <is>
+          <t>UC-071</t>
+        </is>
+      </c>
+      <c r="C92" s="31" t="inlineStr">
+        <is>
+          <t>Question review history</t>
+        </is>
+      </c>
+      <c r="D92" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E92" s="31" t="inlineStr">
+        <is>
+          <t>content.routes review-history returning who changed what and when.</t>
+        </is>
+      </c>
+      <c r="F92" s="31" t="inlineStr">
+        <is>
+          <t>Given a question, when its history is requested, then every transition is listed in order with its actor.</t>
+        </is>
+      </c>
+      <c r="G92" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H92" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I92" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J92" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K92" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L92" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M92" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="93" s="16">
+      <c r="A93" s="24">
+        <f>"TASK-"&amp;TEXT(92,"000")</f>
+        <v/>
+      </c>
+      <c r="B93" s="31" t="inlineStr">
+        <is>
+          <t>UC-072</t>
+        </is>
+      </c>
+      <c r="C93" s="31" t="inlineStr">
+        <is>
+          <t>Content health report</t>
+        </is>
+      </c>
+      <c r="D93" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E93" s="31" t="inlineStr">
+        <is>
+          <t>content.routes content-health, read alongside docs/POOL_CENSUS.md for pool coverage.</t>
+        </is>
+      </c>
+      <c r="F93" s="31" t="inlineStr">
+        <is>
+          <t>Given the report, when it is generated, then scopes below the coverage threshold are listed.</t>
+        </is>
+      </c>
+      <c r="G93" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H93" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I93" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J93" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K93" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L93" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M93" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="94" s="16">
+      <c r="A94" s="24">
+        <f>"TASK-"&amp;TEXT(93,"000")</f>
+        <v/>
+      </c>
+      <c r="B94" s="31" t="inlineStr">
+        <is>
+          <t>UC-073</t>
+        </is>
+      </c>
+      <c r="C94" s="31" t="inlineStr">
+        <is>
+          <t>Question bank search API</t>
+        </is>
+      </c>
+      <c r="D94" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E94" s="31" t="inlineStr">
+        <is>
+          <t>GET /questions with a Zod-validated query over the ~1,400-row bank.</t>
+        </is>
+      </c>
+      <c r="F94" s="31" t="inlineStr">
+        <is>
+          <t>Given filters on scope, state and difficulty, when the endpoint is called, then only matching questions are returned.</t>
+        </is>
+      </c>
+      <c r="G94" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H94" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I94" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J94" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K94" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L94" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M94" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="95" s="16">
+      <c r="A95" s="24">
+        <f>"TASK-"&amp;TEXT(94,"000")</f>
+        <v/>
+      </c>
+      <c r="B95" s="31" t="inlineStr">
+        <is>
+          <t>UC-073</t>
+        </is>
+      </c>
+      <c r="C95" s="31" t="inlineStr">
+        <is>
+          <t>Question bank admin screen</t>
+        </is>
+      </c>
+      <c r="D95" s="31" t="inlineStr">
+        <is>
+          <t>Frontend</t>
+        </is>
+      </c>
+      <c r="E95" s="31" t="inlineStr">
+        <is>
+          <t>Admin UI over GET /questions so content managers can work the bank without direct API calls.</t>
+        </is>
+      </c>
+      <c r="F95" s="31" t="inlineStr">
+        <is>
+          <t>Given the Content tab, when filters are applied, then matching questions render with their lifecycle state and actions.</t>
+        </is>
+      </c>
+      <c r="G95" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H95" s="31" t="inlineStr">
+        <is>
+          <t>FE Dev</t>
+        </is>
+      </c>
+      <c r="I95" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J95" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K95" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L95" s="33" t="n">
+        <v>46315</v>
+      </c>
+      <c r="M95" s="33" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="96" s="16">
+      <c r="A96" s="24">
+        <f>"TASK-"&amp;TEXT(95,"000")</f>
+        <v/>
+      </c>
+      <c r="B96" s="31" t="inlineStr">
+        <is>
+          <t>UC-070</t>
+        </is>
+      </c>
+      <c r="C96" s="31" t="inlineStr">
+        <is>
+          <t>Pool-sufficiency validation at publish time (DB-02)</t>
+        </is>
+      </c>
+      <c r="D96" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E96" s="31" t="inlineStr">
+        <is>
+          <t>Reject a fixed paper whose blueprint the live pool cannot satisfy. Parked until ingestFixedPaper gets a real admin route — it has no live callers today.</t>
+        </is>
+      </c>
+      <c r="F96" s="31" t="inlineStr">
+        <is>
+          <t>Given a blueprint the pool cannot satisfy, when publish is attempted, then it is refused with the shortfall named.</t>
+        </is>
+      </c>
+      <c r="G96" s="31" t="inlineStr">
+        <is>
+          <t>Backlog</t>
+        </is>
+      </c>
+      <c r="H96" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I96" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J96" s="31" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K96" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L96" s="33" t="n"/>
+      <c r="M96" s="33" t="n"/>
+    </row>
+    <row r="97" s="16">
+      <c r="A97" s="24">
+        <f>"TASK-"&amp;TEXT(96,"000")</f>
+        <v/>
+      </c>
+      <c r="B97" s="31" t="inlineStr">
+        <is>
+          <t>UC-074</t>
+        </is>
+      </c>
+      <c r="C97" s="31" t="inlineStr">
+        <is>
+          <t>Reproducible question batch import</t>
+        </is>
+      </c>
+      <c r="D97" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E97" s="31" t="inlineStr">
+        <is>
+          <t>schemas/ plus db/scripts/ import with dry-run reports and error triage in docs/CL2_*.</t>
+        </is>
+      </c>
+      <c r="F97" s="31" t="inlineStr">
+        <is>
+          <t>Given an authored batch, when it is imported, then the dry-run report matches the applied result and images resolve.</t>
+        </is>
+      </c>
+      <c r="G97" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H97" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I97" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J97" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K97" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L97" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M97" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="98" s="16">
+      <c r="A98" s="24">
+        <f>"TASK-"&amp;TEXT(97,"000")</f>
+        <v/>
+      </c>
+      <c r="B98" s="31" t="inlineStr">
+        <is>
+          <t>UC-075</t>
+        </is>
+      </c>
+      <c r="C98" s="31" t="inlineStr">
+        <is>
+          <t>Promote duplicate detection into the publish gate</t>
+        </is>
+      </c>
+      <c r="D98" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E98" s="31" t="inlineStr">
+        <is>
+          <t>Fingerprint normaliser and quarantine exist (db/content/_quarantine, QUESTION_DEDUP_* docs); make a near-duplicate block publication rather than only being reported.</t>
+        </is>
+      </c>
+      <c r="F98" s="31" t="inlineStr">
+        <is>
+          <t>Given a near-duplicate above the agreed threshold, when publish is attempted, then it is quarantined with its match named.</t>
+        </is>
+      </c>
+      <c r="G98" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H98" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I98" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J98" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K98" s="31" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="L98" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M98" s="33" t="n">
+        <v>46284</v>
+      </c>
+    </row>
+    <row r="99" s="16">
+      <c r="A99" s="24">
+        <f>"TASK-"&amp;TEXT(98,"000")</f>
+        <v/>
+      </c>
+      <c r="B99" s="31" t="inlineStr">
+        <is>
+          <t>UC-075</t>
+        </is>
+      </c>
+      <c r="C99" s="31" t="inlineStr">
+        <is>
+          <t>Stem-level duplicate protection in anti-repeat (REP-24)</t>
+        </is>
+      </c>
+      <c r="D99" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E99" s="31" t="inlineStr">
+        <is>
+          <t>Anti-repeat is keyed on question_id, so the same stem under two ids can still reach one student — key the exposure ledger on content fingerprint too.</t>
+        </is>
+      </c>
+      <c r="F99" s="31" t="inlineStr">
+        <is>
+          <t>Given two ids sharing a fingerprint, when papers are assembled for one student, then only one of them is served.</t>
+        </is>
+      </c>
+      <c r="G99" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H99" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I99" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J99" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K99" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L99" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="M99" s="33" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="100" s="16">
+      <c r="A100" s="24">
+        <f>"TASK-"&amp;TEXT(99,"000")</f>
+        <v/>
+      </c>
+      <c r="B100" s="31" t="inlineStr">
+        <is>
+          <t>UC-075</t>
+        </is>
+      </c>
+      <c r="C100" s="31" t="inlineStr">
+        <is>
+          <t>Backfill a dedupe scan across the live bank</t>
+        </is>
+      </c>
+      <c r="D100" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E100" s="31" t="inlineStr">
+        <is>
+          <t>Run the fingerprint scan over all ~1,400 rows and triage the matches into the tracker.</t>
+        </is>
+      </c>
+      <c r="F100" s="31" t="inlineStr">
+        <is>
+          <t>Given the full bank, when the scan completes, then every match is triaged as duplicate or distinct in QUESTION_DEDUP_TRACKER.md.</t>
+        </is>
+      </c>
+      <c r="G100" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H100" s="31" t="inlineStr">
+        <is>
+          <t>Content Ops</t>
+        </is>
+      </c>
+      <c r="I100" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J100" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K100" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L100" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M100" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="101" s="16">
+      <c r="A101" s="24">
+        <f>"TASK-"&amp;TEXT(100,"000")</f>
+        <v/>
+      </c>
+      <c r="B101" s="31" t="inlineStr">
+        <is>
+          <t>UC-076</t>
+        </is>
+      </c>
+      <c r="C101" s="31" t="inlineStr">
+        <is>
+          <t>Reliable question image serving</t>
+        </is>
+      </c>
+      <c r="D101" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E101" s="31" t="inlineStr">
+        <is>
+          <t>asset-resolver with QuestionImage reserving space and framing consistently.</t>
+        </is>
+      </c>
+      <c r="F101" s="31" t="inlineStr">
+        <is>
+          <t>Given an image question, when it renders, then the image loads or a clear fallback is shown, with no layout shift.</t>
+        </is>
+      </c>
+      <c r="G101" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H101" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I101" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J101" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K101" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L101" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M101" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="102" s="16">
+      <c r="A102" s="24">
+        <f>"TASK-"&amp;TEXT(101,"000")</f>
+        <v/>
+      </c>
+      <c r="B102" s="31" t="inlineStr">
+        <is>
+          <t>UC-076</t>
+        </is>
+      </c>
+      <c r="C102" s="31" t="inlineStr">
+        <is>
+          <t>Layout check for long-text and tall-image questions (DB-04)</t>
+        </is>
+      </c>
+      <c r="D102" s="31" t="inlineStr">
+        <is>
+          <t>QA/Testing</t>
+        </is>
+      </c>
+      <c r="E102" s="31" t="inlineStr">
+        <is>
+          <t>The 3 question types x 3 widths matrix was only verified with short text-only MCQs; seed or find an 800-word question and a tall portrait image and re-run the layout check.</t>
+        </is>
+      </c>
+      <c r="F102" s="31" t="inlineStr">
+        <is>
+          <t>Given each of the nine combinations, when it is opened at 1920/1366/390px, then the window itself never scrolls and the nav stays visible.</t>
+        </is>
+      </c>
+      <c r="G102" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 2</t>
+        </is>
+      </c>
+      <c r="H102" s="31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I102" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J102" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K102" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L102" s="33" t="n">
+        <v>46287</v>
+      </c>
+      <c r="M102" s="33" t="n">
+        <v>46298</v>
+      </c>
+    </row>
+    <row r="103" s="16">
+      <c r="A103" s="24">
+        <f>"TASK-"&amp;TEXT(102,"000")</f>
+        <v/>
+      </c>
+      <c r="B103" s="31" t="inlineStr">
+        <is>
+          <t>UC-077</t>
+        </is>
+      </c>
+      <c r="C103" s="31" t="inlineStr">
+        <is>
+          <t>Migrations with matching verification scripts</t>
+        </is>
+      </c>
+      <c r="D103" s="31" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="E103" s="31" t="inlineStr">
+        <is>
+          <t>db/migrations 000-017 each paired with a db/verify script; the Prisma migration track is deliberately unused for this schema.</t>
+        </is>
+      </c>
+      <c r="F103" s="31" t="inlineStr">
+        <is>
+          <t>Given a migration, when its verify script runs, then the live schema is proven to match rather than assumed.</t>
+        </is>
+      </c>
+      <c r="G103" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H103" s="31" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="I103" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J103" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K103" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L103" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M103" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="104" s="16">
+      <c r="A104" s="24">
+        <f>"TASK-"&amp;TEXT(103,"000")</f>
+        <v/>
+      </c>
+      <c r="B104" s="31" t="inlineStr">
+        <is>
+          <t>UC-078</t>
+        </is>
+      </c>
+      <c r="C104" s="31" t="inlineStr">
+        <is>
+          <t>Ordered environment seed scripts</t>
+        </is>
+      </c>
+      <c r="D104" s="31" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="E104" s="31" t="inlineStr">
+        <is>
+          <t>db/scripts/seed/* in the sequence documented in README.md and docs/CORE_LAYER_OPERATIONS.md.</t>
+        </is>
+      </c>
+      <c r="F104" s="31" t="inlineStr">
+        <is>
+          <t>Given an empty database, when the seeds run in order, then the environment reaches a usable state with a working demo account.</t>
+        </is>
+      </c>
+      <c r="G104" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H104" s="31" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="I104" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J104" s="31" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K104" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L104" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M104" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="105" s="16">
+      <c r="A105" s="24">
+        <f>"TASK-"&amp;TEXT(104,"000")</f>
+        <v/>
+      </c>
+      <c r="B105" s="31" t="inlineStr">
+        <is>
+          <t>UC-079</t>
+        </is>
+      </c>
+      <c r="C105" s="31" t="inlineStr">
+        <is>
+          <t>Service health endpoint</t>
+        </is>
+      </c>
+      <c r="D105" s="31" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="E105" s="31" t="inlineStr">
+        <is>
+          <t>GET /health reporting whether the service is actually serving, not just up.</t>
+        </is>
+      </c>
+      <c r="F105" s="31" t="inlineStr">
+        <is>
+          <t>Given a degraded dependency, when /health is polled, then it reports unhealthy rather than 200.</t>
+        </is>
+      </c>
+      <c r="G105" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H105" s="31" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="I105" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="J105" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K105" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L105" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M105" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="106" s="16">
+      <c r="A106" s="24">
+        <f>"TASK-"&amp;TEXT(105,"000")</f>
+        <v/>
+      </c>
+      <c r="B106" s="31" t="inlineStr">
+        <is>
+          <t>UC-079</t>
+        </is>
+      </c>
+      <c r="C106" s="31" t="inlineStr">
+        <is>
+          <t>Container healthcheck and uptime alerting</t>
+        </is>
+      </c>
+      <c r="D106" s="31" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="E106" s="31" t="inlineStr">
+        <is>
+          <t>Wire the Dockerfile healthcheck sketched in docs/FRONTEND.md sec 4.2 and alert on repeated failures.</t>
+        </is>
+      </c>
+      <c r="F106" s="31" t="inlineStr">
+        <is>
+          <t>Given a failing health endpoint, when the threshold is crossed, then the container is marked unhealthy and an alert fires.</t>
+        </is>
+      </c>
+      <c r="G106" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 4</t>
+        </is>
+      </c>
+      <c r="H106" s="31" t="inlineStr">
+        <is>
+          <t>DevOps</t>
+        </is>
+      </c>
+      <c r="I106" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J106" s="31" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K106" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L106" s="33" t="n">
+        <v>46315</v>
+      </c>
+      <c r="M106" s="33" t="n">
+        <v>46326</v>
+      </c>
+    </row>
+    <row r="107" s="16">
+      <c r="A107" s="24">
+        <f>"TASK-"&amp;TEXT(106,"000")</f>
+        <v/>
+      </c>
+      <c r="B107" s="31" t="inlineStr">
+        <is>
+          <t>UC-080</t>
+        </is>
+      </c>
+      <c r="C107" s="31" t="inlineStr">
+        <is>
+          <t>Permission gating on every privileged route</t>
+        </is>
+      </c>
+      <c r="D107" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E107" s="31" t="inlineStr">
+        <is>
+          <t>middleware/requireAuth and requirePermission; there is no JWT_SECRET in the app by design.</t>
+        </is>
+      </c>
+      <c r="F107" s="31" t="inlineStr">
+        <is>
+          <t>Given a role without a permission, when a gated route is called, then it is refused with 403 and nothing is mutated.</t>
+        </is>
+      </c>
+      <c r="G107" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H107" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I107" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J107" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K107" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L107" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M107" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="108" s="16">
+      <c r="A108" s="24">
+        <f>"TASK-"&amp;TEXT(107,"000")</f>
+        <v/>
+      </c>
+      <c r="B108" s="31" t="inlineStr">
+        <is>
+          <t>UC-081</t>
+        </is>
+      </c>
+      <c r="C108" s="31" t="inlineStr">
+        <is>
+          <t>Ownership checks on user-scoped data</t>
+        </is>
+      </c>
+      <c r="D108" s="31" t="inlineStr">
+        <is>
+          <t>Backend</t>
+        </is>
+      </c>
+      <c r="E108" s="31" t="inlineStr">
+        <is>
+          <t>middleware/ownership.ts with lib/dbCrudRouter; audit_log stays out of CRUD as append-only.</t>
+        </is>
+      </c>
+      <c r="F108" s="31" t="inlineStr">
+        <is>
+          <t>Given another student's attempt, plan or deck id, when it is requested, then the call is refused.</t>
+        </is>
+      </c>
+      <c r="G108" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 1</t>
+        </is>
+      </c>
+      <c r="H108" s="31" t="inlineStr">
+        <is>
+          <t>BE Dev</t>
+        </is>
+      </c>
+      <c r="I108" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="J108" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K108" s="31" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L108" s="33" t="n">
+        <v>46273</v>
+      </c>
+      <c r="M108" s="33" t="n">
+        <v>46277</v>
+      </c>
+    </row>
+    <row r="109" s="16">
+      <c r="A109" s="24">
+        <f>"TASK-"&amp;TEXT(108,"000")</f>
+        <v/>
+      </c>
+      <c r="B109" s="31" t="inlineStr">
+        <is>
+          <t>UC-080</t>
+        </is>
+      </c>
+      <c r="C109" s="31" t="inlineStr">
+        <is>
+          <t>Permission and ownership regression suite</t>
+        </is>
+      </c>
+      <c r="D109" s="31" t="inlineStr">
+        <is>
+          <t>QA/Testing</t>
+        </is>
+      </c>
+      <c r="E109" s="31" t="inlineStr">
+        <is>
+          <t>One automated case per gated route asserting the refusal, so a role change cannot silently open access.</t>
+        </is>
+      </c>
+      <c r="F109" s="31" t="inlineStr">
+        <is>
+          <t>Given the suite, when it runs in CI, then every gated route has a passing negative case.</t>
+        </is>
+      </c>
+      <c r="G109" s="31" t="inlineStr">
+        <is>
+          <t>Sprint 3</t>
+        </is>
+      </c>
+      <c r="H109" s="31" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="I109" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="J109" s="31" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K109" s="31" t="inlineStr">
+        <is>
+          <t>To Do</t>
+        </is>
+      </c>
+      <c r="L109" s="33" t="n">
+        <v>46301</v>
+      </c>
+      <c r="M109" s="33" t="n">
+        <v>46312</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="24">
+        <f>"TASK-"&amp;TEXT(109,"000")</f>
+        <v/>
+      </c>
+      <c r="B110" s="25" t="n"/>
+      <c r="C110" s="25" t="n"/>
+      <c r="D110" s="25" t="n"/>
+      <c r="E110" s="25" t="n"/>
+      <c r="F110" s="25" t="n"/>
+      <c r="G110" s="25" t="n"/>
+      <c r="H110" s="25" t="n"/>
+      <c r="I110" s="27" t="n"/>
+      <c r="J110" s="25" t="n"/>
+      <c r="K110" s="25" t="n"/>
+      <c r="L110" s="28" t="n"/>
+      <c r="M110" s="28" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="24">
+        <f>"TASK-"&amp;TEXT(110,"000")</f>
+        <v/>
+      </c>
+      <c r="B111" s="25" t="n"/>
+      <c r="C111" s="25" t="n"/>
+      <c r="D111" s="25" t="n"/>
+      <c r="E111" s="25" t="n"/>
+      <c r="F111" s="25" t="n"/>
+      <c r="G111" s="25" t="n"/>
+      <c r="H111" s="25" t="n"/>
+      <c r="I111" s="27" t="n"/>
+      <c r="J111" s="25" t="n"/>
+      <c r="K111" s="25" t="n"/>
+      <c r="L111" s="28" t="n"/>
+      <c r="M111" s="28" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="24">
+        <f>"TASK-"&amp;TEXT(111,"000")</f>
+        <v/>
+      </c>
+      <c r="B112" s="25" t="n"/>
+      <c r="C112" s="25" t="n"/>
+      <c r="D112" s="25" t="n"/>
+      <c r="E112" s="25" t="n"/>
+      <c r="F112" s="25" t="n"/>
+      <c r="G112" s="25" t="n"/>
+      <c r="H112" s="25" t="n"/>
+      <c r="I112" s="27" t="n"/>
+      <c r="J112" s="25" t="n"/>
+      <c r="K112" s="25" t="n"/>
+      <c r="L112" s="28" t="n"/>
+      <c r="M112" s="28" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="24">
+        <f>"TASK-"&amp;TEXT(112,"000")</f>
+        <v/>
+      </c>
+      <c r="B113" s="25" t="n"/>
+      <c r="C113" s="25" t="n"/>
+      <c r="D113" s="25" t="n"/>
+      <c r="E113" s="25" t="n"/>
+      <c r="F113" s="25" t="n"/>
+      <c r="G113" s="25" t="n"/>
+      <c r="H113" s="25" t="n"/>
+      <c r="I113" s="27" t="n"/>
+      <c r="J113" s="25" t="n"/>
+      <c r="K113" s="25" t="n"/>
+      <c r="L113" s="28" t="n"/>
+      <c r="M113" s="28" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="24">
+        <f>"TASK-"&amp;TEXT(113,"000")</f>
+        <v/>
+      </c>
+      <c r="B114" s="25" t="n"/>
+      <c r="C114" s="25" t="n"/>
+      <c r="D114" s="25" t="n"/>
+      <c r="E114" s="25" t="n"/>
+      <c r="F114" s="25" t="n"/>
+      <c r="G114" s="25" t="n"/>
+      <c r="H114" s="25" t="n"/>
+      <c r="I114" s="27" t="n"/>
+      <c r="J114" s="25" t="n"/>
+      <c r="K114" s="25" t="n"/>
+      <c r="L114" s="28" t="n"/>
+      <c r="M114" s="28" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="24">
+        <f>"TASK-"&amp;TEXT(114,"000")</f>
+        <v/>
+      </c>
+      <c r="B115" s="25" t="n"/>
+      <c r="C115" s="25" t="n"/>
+      <c r="D115" s="25" t="n"/>
+      <c r="E115" s="25" t="n"/>
+      <c r="F115" s="25" t="n"/>
+      <c r="G115" s="25" t="n"/>
+      <c r="H115" s="25" t="n"/>
+      <c r="I115" s="27" t="n"/>
+      <c r="J115" s="25" t="n"/>
+      <c r="K115" s="25" t="n"/>
+      <c r="L115" s="28" t="n"/>
+      <c r="M115" s="28" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="24">
+        <f>"TASK-"&amp;TEXT(115,"000")</f>
+        <v/>
+      </c>
+      <c r="B116" s="25" t="n"/>
+      <c r="C116" s="25" t="n"/>
+      <c r="D116" s="25" t="n"/>
+      <c r="E116" s="25" t="n"/>
+      <c r="F116" s="25" t="n"/>
+      <c r="G116" s="25" t="n"/>
+      <c r="H116" s="25" t="n"/>
+      <c r="I116" s="27" t="n"/>
+      <c r="J116" s="25" t="n"/>
+      <c r="K116" s="25" t="n"/>
+      <c r="L116" s="28" t="n"/>
+      <c r="M116" s="28" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="24">
+        <f>"TASK-"&amp;TEXT(116,"000")</f>
+        <v/>
+      </c>
+      <c r="B117" s="25" t="n"/>
+      <c r="C117" s="25" t="n"/>
+      <c r="D117" s="25" t="n"/>
+      <c r="E117" s="25" t="n"/>
+      <c r="F117" s="25" t="n"/>
+      <c r="G117" s="25" t="n"/>
+      <c r="H117" s="25" t="n"/>
+      <c r="I117" s="27" t="n"/>
+      <c r="J117" s="25" t="n"/>
+      <c r="K117" s="25" t="n"/>
+      <c r="L117" s="28" t="n"/>
+      <c r="M117" s="28" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="24">
+        <f>"TASK-"&amp;TEXT(117,"000")</f>
+        <v/>
+      </c>
+      <c r="B118" s="25" t="n"/>
+      <c r="C118" s="25" t="n"/>
+      <c r="D118" s="25" t="n"/>
+      <c r="E118" s="25" t="n"/>
+      <c r="F118" s="25" t="n"/>
+      <c r="G118" s="25" t="n"/>
+      <c r="H118" s="25" t="n"/>
+      <c r="I118" s="27" t="n"/>
+      <c r="J118" s="25" t="n"/>
+      <c r="K118" s="25" t="n"/>
+      <c r="L118" s="28" t="n"/>
+      <c r="M118" s="28" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="24">
+        <f>"TASK-"&amp;TEXT(118,"000")</f>
+        <v/>
+      </c>
+      <c r="B119" s="25" t="n"/>
+      <c r="C119" s="25" t="n"/>
+      <c r="D119" s="25" t="n"/>
+      <c r="E119" s="25" t="n"/>
+      <c r="F119" s="25" t="n"/>
+      <c r="G119" s="25" t="n"/>
+      <c r="H119" s="25" t="n"/>
+      <c r="I119" s="27" t="n"/>
+      <c r="J119" s="25" t="n"/>
+      <c r="K119" s="25" t="n"/>
+      <c r="L119" s="28" t="n"/>
+      <c r="M119" s="28" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="24">
+        <f>"TASK-"&amp;TEXT(119,"000")</f>
+        <v/>
+      </c>
+      <c r="B120" s="25" t="n"/>
+      <c r="C120" s="25" t="n"/>
+      <c r="D120" s="25" t="n"/>
+      <c r="E120" s="25" t="n"/>
+      <c r="F120" s="25" t="n"/>
+      <c r="G120" s="25" t="n"/>
+      <c r="H120" s="25" t="n"/>
+      <c r="I120" s="27" t="n"/>
+      <c r="J120" s="25" t="n"/>
+      <c r="K120" s="25" t="n"/>
+      <c r="L120" s="28" t="n"/>
+      <c r="M120" s="28" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="24">
+        <f>"TASK-"&amp;TEXT(120,"000")</f>
+        <v/>
+      </c>
+      <c r="B121" s="25" t="n"/>
+      <c r="C121" s="25" t="n"/>
+      <c r="D121" s="25" t="n"/>
+      <c r="E121" s="25" t="n"/>
+      <c r="F121" s="25" t="n"/>
+      <c r="G121" s="25" t="n"/>
+      <c r="H121" s="25" t="n"/>
+      <c r="I121" s="27" t="n"/>
+      <c r="J121" s="25" t="n"/>
+      <c r="K121" s="25" t="n"/>
+      <c r="L121" s="28" t="n"/>
+      <c r="M121" s="28" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:M121"/>
   <dataValidations count="4">
-    <dataValidation sqref="J3:J42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="J3:J121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lookup Lists'!$A$2:$A$5</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="K3:K42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="K3:K121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lookup Lists'!$C$2:$C$6</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="D3:D42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="D3:D121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lookup Lists'!$D$2:$D$9</formula1>
-      <formula2>0</formula2>
     </dataValidation>
-    <dataValidation sqref="G3:G42" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list" errorStyle="stop" operator="between">
+    <dataValidation sqref="G3:G121" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>'Lookup Lists'!$E$2:$E$7</formula1>
-      <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -6627,7 +12545,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="B2:I11"/>
+  <dimension ref="A2:I11"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="15" min="1" max="1"/>
@@ -6691,31 +12609,31 @@
         </is>
       </c>
       <c r="C5" s="29">
-        <f>COUNTIF('Sprint Tasks'!$G$3:$G$42,$B5)</f>
+        <f>COUNTIF('Sprint Tasks'!$G$3:$G$121,$B5)</f>
         <v/>
       </c>
       <c r="D5" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B5,'Sprint Tasks'!$K$3:$K$42,"To Do")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B5,'Sprint Tasks'!$K$3:$K$121,"To Do")</f>
         <v/>
       </c>
       <c r="E5" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B5,'Sprint Tasks'!$K$3:$K$42,"In Progress")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B5,'Sprint Tasks'!$K$3:$K$121,"In Progress")</f>
         <v/>
       </c>
       <c r="F5" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B5,'Sprint Tasks'!$K$3:$K$42,"In Review")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B5,'Sprint Tasks'!$K$3:$K$121,"In Review")</f>
         <v/>
       </c>
       <c r="G5" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B5,'Sprint Tasks'!$K$3:$K$42,"Blocked")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B5,'Sprint Tasks'!$K$3:$K$121,"Blocked")</f>
         <v/>
       </c>
       <c r="H5" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B5,'Sprint Tasks'!$K$3:$K$42,"Done")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B5,'Sprint Tasks'!$K$3:$K$121,"Done")</f>
         <v/>
       </c>
       <c r="I5" s="29">
-        <f>SUMIF('Sprint Tasks'!$G$3:$G$42,$B5,'Sprint Tasks'!$I$3:$I$42)</f>
+        <f>SUMIF('Sprint Tasks'!$G$3:$G$121,$B5,'Sprint Tasks'!$I$3:$I$121)</f>
         <v/>
       </c>
     </row>
@@ -6726,31 +12644,31 @@
         </is>
       </c>
       <c r="C6" s="29">
-        <f>COUNTIF('Sprint Tasks'!$G$3:$G$42,$B6)</f>
+        <f>COUNTIF('Sprint Tasks'!$G$3:$G$121,$B6)</f>
         <v/>
       </c>
       <c r="D6" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B6,'Sprint Tasks'!$K$3:$K$42,"To Do")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B6,'Sprint Tasks'!$K$3:$K$121,"To Do")</f>
         <v/>
       </c>
       <c r="E6" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B6,'Sprint Tasks'!$K$3:$K$42,"In Progress")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B6,'Sprint Tasks'!$K$3:$K$121,"In Progress")</f>
         <v/>
       </c>
       <c r="F6" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B6,'Sprint Tasks'!$K$3:$K$42,"In Review")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B6,'Sprint Tasks'!$K$3:$K$121,"In Review")</f>
         <v/>
       </c>
       <c r="G6" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B6,'Sprint Tasks'!$K$3:$K$42,"Blocked")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B6,'Sprint Tasks'!$K$3:$K$121,"Blocked")</f>
         <v/>
       </c>
       <c r="H6" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B6,'Sprint Tasks'!$K$3:$K$42,"Done")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B6,'Sprint Tasks'!$K$3:$K$121,"Done")</f>
         <v/>
       </c>
       <c r="I6" s="29">
-        <f>SUMIF('Sprint Tasks'!$G$3:$G$42,$B6,'Sprint Tasks'!$I$3:$I$42)</f>
+        <f>SUMIF('Sprint Tasks'!$G$3:$G$121,$B6,'Sprint Tasks'!$I$3:$I$121)</f>
         <v/>
       </c>
     </row>
@@ -6761,31 +12679,31 @@
         </is>
       </c>
       <c r="C7" s="29">
-        <f>COUNTIF('Sprint Tasks'!$G$3:$G$42,$B7)</f>
+        <f>COUNTIF('Sprint Tasks'!$G$3:$G$121,$B7)</f>
         <v/>
       </c>
       <c r="D7" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B7,'Sprint Tasks'!$K$3:$K$42,"To Do")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B7,'Sprint Tasks'!$K$3:$K$121,"To Do")</f>
         <v/>
       </c>
       <c r="E7" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B7,'Sprint Tasks'!$K$3:$K$42,"In Progress")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B7,'Sprint Tasks'!$K$3:$K$121,"In Progress")</f>
         <v/>
       </c>
       <c r="F7" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B7,'Sprint Tasks'!$K$3:$K$42,"In Review")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B7,'Sprint Tasks'!$K$3:$K$121,"In Review")</f>
         <v/>
       </c>
       <c r="G7" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B7,'Sprint Tasks'!$K$3:$K$42,"Blocked")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B7,'Sprint Tasks'!$K$3:$K$121,"Blocked")</f>
         <v/>
       </c>
       <c r="H7" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B7,'Sprint Tasks'!$K$3:$K$42,"Done")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B7,'Sprint Tasks'!$K$3:$K$121,"Done")</f>
         <v/>
       </c>
       <c r="I7" s="29">
-        <f>SUMIF('Sprint Tasks'!$G$3:$G$42,$B7,'Sprint Tasks'!$I$3:$I$42)</f>
+        <f>SUMIF('Sprint Tasks'!$G$3:$G$121,$B7,'Sprint Tasks'!$I$3:$I$121)</f>
         <v/>
       </c>
     </row>
@@ -6796,31 +12714,31 @@
         </is>
       </c>
       <c r="C8" s="29">
-        <f>COUNTIF('Sprint Tasks'!$G$3:$G$42,$B8)</f>
+        <f>COUNTIF('Sprint Tasks'!$G$3:$G$121,$B8)</f>
         <v/>
       </c>
       <c r="D8" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B8,'Sprint Tasks'!$K$3:$K$42,"To Do")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B8,'Sprint Tasks'!$K$3:$K$121,"To Do")</f>
         <v/>
       </c>
       <c r="E8" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B8,'Sprint Tasks'!$K$3:$K$42,"In Progress")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B8,'Sprint Tasks'!$K$3:$K$121,"In Progress")</f>
         <v/>
       </c>
       <c r="F8" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B8,'Sprint Tasks'!$K$3:$K$42,"In Review")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B8,'Sprint Tasks'!$K$3:$K$121,"In Review")</f>
         <v/>
       </c>
       <c r="G8" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B8,'Sprint Tasks'!$K$3:$K$42,"Blocked")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B8,'Sprint Tasks'!$K$3:$K$121,"Blocked")</f>
         <v/>
       </c>
       <c r="H8" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B8,'Sprint Tasks'!$K$3:$K$42,"Done")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B8,'Sprint Tasks'!$K$3:$K$121,"Done")</f>
         <v/>
       </c>
       <c r="I8" s="29">
-        <f>SUMIF('Sprint Tasks'!$G$3:$G$42,$B8,'Sprint Tasks'!$I$3:$I$42)</f>
+        <f>SUMIF('Sprint Tasks'!$G$3:$G$121,$B8,'Sprint Tasks'!$I$3:$I$121)</f>
         <v/>
       </c>
     </row>
@@ -6831,31 +12749,31 @@
         </is>
       </c>
       <c r="C9" s="29">
-        <f>COUNTIF('Sprint Tasks'!$G$3:$G$42,$B9)</f>
+        <f>COUNTIF('Sprint Tasks'!$G$3:$G$121,$B9)</f>
         <v/>
       </c>
       <c r="D9" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B9,'Sprint Tasks'!$K$3:$K$42,"To Do")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B9,'Sprint Tasks'!$K$3:$K$121,"To Do")</f>
         <v/>
       </c>
       <c r="E9" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B9,'Sprint Tasks'!$K$3:$K$42,"In Progress")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B9,'Sprint Tasks'!$K$3:$K$121,"In Progress")</f>
         <v/>
       </c>
       <c r="F9" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B9,'Sprint Tasks'!$K$3:$K$42,"In Review")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B9,'Sprint Tasks'!$K$3:$K$121,"In Review")</f>
         <v/>
       </c>
       <c r="G9" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B9,'Sprint Tasks'!$K$3:$K$42,"Blocked")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B9,'Sprint Tasks'!$K$3:$K$121,"Blocked")</f>
         <v/>
       </c>
       <c r="H9" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B9,'Sprint Tasks'!$K$3:$K$42,"Done")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B9,'Sprint Tasks'!$K$3:$K$121,"Done")</f>
         <v/>
       </c>
       <c r="I9" s="29">
-        <f>SUMIF('Sprint Tasks'!$G$3:$G$42,$B9,'Sprint Tasks'!$I$3:$I$42)</f>
+        <f>SUMIF('Sprint Tasks'!$G$3:$G$121,$B9,'Sprint Tasks'!$I$3:$I$121)</f>
         <v/>
       </c>
     </row>
@@ -6866,31 +12784,31 @@
         </is>
       </c>
       <c r="C10" s="29">
-        <f>COUNTIF('Sprint Tasks'!$G$3:$G$42,$B10)</f>
+        <f>COUNTIF('Sprint Tasks'!$G$3:$G$121,$B10)</f>
         <v/>
       </c>
       <c r="D10" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B10,'Sprint Tasks'!$K$3:$K$42,"To Do")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B10,'Sprint Tasks'!$K$3:$K$121,"To Do")</f>
         <v/>
       </c>
       <c r="E10" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B10,'Sprint Tasks'!$K$3:$K$42,"In Progress")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B10,'Sprint Tasks'!$K$3:$K$121,"In Progress")</f>
         <v/>
       </c>
       <c r="F10" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B10,'Sprint Tasks'!$K$3:$K$42,"In Review")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B10,'Sprint Tasks'!$K$3:$K$121,"In Review")</f>
         <v/>
       </c>
       <c r="G10" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B10,'Sprint Tasks'!$K$3:$K$42,"Blocked")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B10,'Sprint Tasks'!$K$3:$K$121,"Blocked")</f>
         <v/>
       </c>
       <c r="H10" s="29">
-        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$42,$B10,'Sprint Tasks'!$K$3:$K$42,"Done")</f>
+        <f>COUNTIFS('Sprint Tasks'!$G$3:$G$121,$B10,'Sprint Tasks'!$K$3:$K$121,"Done")</f>
         <v/>
       </c>
       <c r="I10" s="29">
-        <f>SUMIF('Sprint Tasks'!$G$3:$G$42,$B10,'Sprint Tasks'!$I$3:$I$42)</f>
+        <f>SUMIF('Sprint Tasks'!$G$3:$G$121,$B10,'Sprint Tasks'!$I$3:$I$121)</f>
         <v/>
       </c>
     </row>
